--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$92</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 25/07/2025, Data Final: 18/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 14 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em domingo, 17 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -289,19 +289,22 @@
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
     <t>FA-11476</t>
   </si>
   <si>
     <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
   </si>
   <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
+    <t>FA-11399</t>
   </si>
   <si>
     <t>FA-11615</t>
@@ -310,9 +313,6 @@
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
     <t>FA-11278</t>
   </si>
   <si>
@@ -352,82 +352,91 @@
     <t>A VENCER</t>
   </si>
   <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
     <t>FA-11474</t>
   </si>
   <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
     <t>FA-11525</t>
   </si>
   <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
     <t>FA-11481</t>
   </si>
   <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
   </si>
   <si>
     <t>FA-11616</t>
   </si>
   <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
     <t>FA-11279</t>
   </si>
   <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
     <t>FA-11482</t>
   </si>
   <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
     <t>FA-11433</t>
   </si>
   <si>
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
     <t>FA-11561</t>
   </si>
   <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
   </si>
   <si>
     <t>FA-11268</t>
@@ -436,13 +445,67 @@
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11621</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
+  </si>
+  <si>
+    <t>FA-11613</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
 </sst>
 </file>
@@ -585,7 +648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -702,10 +765,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-38</v>
+        <v>-41</v>
       </c>
       <c r="G6" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -761,10 +824,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G7" s="8">
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -820,10 +883,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-45</v>
+        <v>-48</v>
       </c>
       <c r="G8" s="8">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -879,10 +942,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G9" s="8">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -938,10 +1001,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G10" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -997,10 +1060,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G11" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1056,10 +1119,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G12" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1115,10 +1178,10 @@
         <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G13" s="8">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>25</v>
@@ -1174,10 +1237,10 @@
         <v>23</v>
       </c>
       <c r="F14" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G14" s="8">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>24</v>
@@ -1233,10 +1296,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="G15" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1292,10 +1355,10 @@
         <v>46141</v>
       </c>
       <c r="F16" s="8">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="G16" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1351,10 +1414,10 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G17" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1410,10 +1473,10 @@
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G18" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -1469,10 +1532,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G19" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>24</v>
@@ -1528,10 +1591,10 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G20" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>25</v>
@@ -1587,10 +1650,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G21" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1646,10 +1709,10 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G22" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1705,10 +1768,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G23" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1764,10 +1827,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1823,10 +1886,10 @@
         <v>46119</v>
       </c>
       <c r="F25" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G25" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1882,10 +1945,10 @@
         <v>46141</v>
       </c>
       <c r="F26" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G26" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -1941,10 +2004,10 @@
         <v>46112</v>
       </c>
       <c r="F27" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G27" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>25</v>
@@ -2000,10 +2063,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G28" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2059,10 +2122,10 @@
         <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G29" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2118,10 +2181,10 @@
         <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G30" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2177,10 +2240,10 @@
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="G31" s="8">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2236,10 +2299,10 @@
         <v>46148</v>
       </c>
       <c r="F32" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2295,10 +2358,10 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G33" s="8">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>24</v>
@@ -2354,10 +2417,10 @@
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G34" s="8">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2413,10 +2476,10 @@
         <v>46153</v>
       </c>
       <c r="F35" s="8">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="G35" s="8">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2472,10 +2535,10 @@
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-218</v>
+        <v>-221</v>
       </c>
       <c r="G36" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>78</v>
@@ -2531,10 +2594,10 @@
         <v>46097</v>
       </c>
       <c r="F37" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>25</v>
@@ -2590,10 +2653,10 @@
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>25</v>
@@ -2649,10 +2712,10 @@
         <v>46119</v>
       </c>
       <c r="F39" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2708,10 +2771,10 @@
         <v>46127</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -2764,13 +2827,13 @@
         <v>46153</v>
       </c>
       <c r="E41" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F41" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -2785,10 +2848,10 @@
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>28</v>
@@ -2803,7 +2866,7 @@
         <v>39</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S41" s="9">
         <v>620</v>
@@ -2826,10 +2889,10 @@
         <v>46141</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2838,16 +2901,16 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="M42" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>28</v>
@@ -2882,13 +2945,13 @@
         <v>46153</v>
       </c>
       <c r="E43" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F43" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G43" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -2921,7 +2984,7 @@
         <v>39</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S43" s="9">
         <v>620</v>
@@ -2941,13 +3004,13 @@
         <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="F44" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>25</v>
@@ -2962,7 +3025,7 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -3000,13 +3063,13 @@
         <v>46153</v>
       </c>
       <c r="E45" s="7">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>25</v>
@@ -3015,13 +3078,13 @@
         <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3062,10 +3125,10 @@
         <v>46092</v>
       </c>
       <c r="F46" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G46" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>25</v>
@@ -3121,10 +3184,10 @@
         <v>46119</v>
       </c>
       <c r="F47" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G47" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>25</v>
@@ -3180,10 +3243,10 @@
         <v>46119</v>
       </c>
       <c r="F48" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G48" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>25</v>
@@ -3239,10 +3302,10 @@
         <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G49" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>25</v>
@@ -3298,10 +3361,10 @@
         <v>46141</v>
       </c>
       <c r="F50" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G50" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>25</v>
@@ -3357,10 +3420,10 @@
         <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G51" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3416,10 +3479,10 @@
         <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>24</v>
@@ -3475,10 +3538,10 @@
         <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3493,7 +3556,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3534,10 +3597,10 @@
         <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3593,10 +3656,10 @@
         <v>46097</v>
       </c>
       <c r="F55" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>23</v>
@@ -3649,13 +3712,13 @@
         <v>46160</v>
       </c>
       <c r="E56" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F56" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>23</v>
@@ -3670,10 +3733,10 @@
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>105</v>
@@ -3708,13 +3771,13 @@
         <v>46160</v>
       </c>
       <c r="E57" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F57" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3723,16 +3786,16 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>105</v>
@@ -3770,10 +3833,10 @@
         <v>46127</v>
       </c>
       <c r="F58" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3826,13 +3889,13 @@
         <v>46160</v>
       </c>
       <c r="E59" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F59" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3847,10 +3910,10 @@
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>105</v>
@@ -3865,7 +3928,7 @@
         <v>39</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S59" s="9">
         <v>620</v>
@@ -3888,10 +3951,10 @@
         <v>46141</v>
       </c>
       <c r="F60" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G60" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -3906,10 +3969,10 @@
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>105</v>
@@ -3944,13 +4007,13 @@
         <v>46160</v>
       </c>
       <c r="E61" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F61" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -3983,7 +4046,7 @@
         <v>39</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S61" s="9">
         <v>620</v>
@@ -4003,13 +4066,13 @@
         <v>46160</v>
       </c>
       <c r="E62" s="7">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="F62" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G62" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4024,7 +4087,7 @@
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
@@ -4062,13 +4125,13 @@
         <v>46160</v>
       </c>
       <c r="E63" s="7">
-        <v>46127</v>
+        <v>46112</v>
       </c>
       <c r="F63" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G63" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4077,13 +4140,13 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
@@ -4121,13 +4184,13 @@
         <v>46160</v>
       </c>
       <c r="E64" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F64" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4154,7 +4217,7 @@
         <v>105</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>39</v>
@@ -4180,13 +4243,13 @@
         <v>46160</v>
       </c>
       <c r="E65" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F65" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G65" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4213,7 +4276,7 @@
         <v>105</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q65" s="6" t="s">
         <v>39</v>
@@ -4239,13 +4302,13 @@
         <v>46160</v>
       </c>
       <c r="E66" s="7">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="F66" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G66" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4260,7 +4323,7 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
@@ -4298,13 +4361,13 @@
         <v>46160</v>
       </c>
       <c r="E67" s="7">
-        <v>46092</v>
+        <v>46153</v>
       </c>
       <c r="F67" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4319,7 +4382,7 @@
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
@@ -4360,10 +4423,10 @@
         <v>46127</v>
       </c>
       <c r="F68" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G68" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4416,13 +4479,13 @@
         <v>46160</v>
       </c>
       <c r="E69" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F69" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G69" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4437,10 +4500,10 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
         <v>105</v>
@@ -4475,13 +4538,13 @@
         <v>46160</v>
       </c>
       <c r="E70" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F70" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G70" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4496,10 +4559,10 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N70" s="6" t="s">
         <v>105</v>
@@ -4537,10 +4600,10 @@
         <v>46119</v>
       </c>
       <c r="F71" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G71" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4593,13 +4656,13 @@
         <v>46160</v>
       </c>
       <c r="E72" s="7">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="F72" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4614,10 +4677,10 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N72" s="6" t="s">
         <v>105</v>
@@ -4632,7 +4695,7 @@
         <v>39</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S72" s="9">
         <v>680</v>
@@ -4655,10 +4718,10 @@
         <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4714,10 +4777,10 @@
         <v>46119</v>
       </c>
       <c r="F74" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G74" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4770,13 +4833,13 @@
         <v>46160</v>
       </c>
       <c r="E75" s="7">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="F75" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G75" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4791,10 +4854,10 @@
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
         <v>105</v>
@@ -4809,7 +4872,7 @@
         <v>39</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S75" s="9">
         <v>680</v>
@@ -4829,13 +4892,13 @@
         <v>46160</v>
       </c>
       <c r="E76" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G76" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4850,7 +4913,7 @@
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
@@ -4862,7 +4925,7 @@
         <v>105</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q76" s="6" t="s">
         <v>39</v>
@@ -4891,10 +4954,10 @@
         <v>46099</v>
       </c>
       <c r="F77" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G77" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4903,13 +4966,13 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L77" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
@@ -4947,13 +5010,13 @@
         <v>46160</v>
       </c>
       <c r="E78" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F78" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -4962,14 +5025,14 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
@@ -4980,7 +5043,7 @@
         <v>105</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q78" s="6" t="s">
         <v>39</v>
@@ -4993,62 +5056,1183 @@
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S79" s="13">
-        <f>SUM(S6:S78)</f>
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46161</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F79" s="8">
+        <v>-9</v>
+      </c>
+      <c r="G79" s="8">
+        <v>2</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S79" s="9">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="80" ht="23" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F80" s="8">
+        <v>8</v>
+      </c>
+      <c r="G80" s="8">
+        <v>8</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S80" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="81" ht="23" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F81" s="8">
+        <v>8</v>
+      </c>
+      <c r="G81" s="8">
+        <v>8</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S81" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="82" ht="23" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F82" s="8">
+        <v>8</v>
+      </c>
+      <c r="G82" s="8">
+        <v>8</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S82" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" ht="23" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F83" s="8">
+        <v>8</v>
+      </c>
+      <c r="G83" s="8">
+        <v>8</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S83" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F84" s="8">
+        <v>8</v>
+      </c>
+      <c r="G84" s="8">
+        <v>8</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S84" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F85" s="8">
+        <v>8</v>
+      </c>
+      <c r="G85" s="8">
+        <v>8</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S85" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="86" ht="23" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F86" s="8">
+        <v>8</v>
+      </c>
+      <c r="G86" s="8">
+        <v>8</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S86" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F87" s="8">
+        <v>8</v>
+      </c>
+      <c r="G87" s="8">
+        <v>8</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S87" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F88" s="8">
+        <v>8</v>
+      </c>
+      <c r="G88" s="8">
+        <v>8</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S88" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="89" ht="23" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F89" s="8">
+        <v>8</v>
+      </c>
+      <c r="G89" s="8">
+        <v>8</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S89" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="90" ht="23" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F90" s="8">
+        <v>8</v>
+      </c>
+      <c r="G90" s="8">
+        <v>8</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S90" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="91" ht="23" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F91" s="8">
+        <v>8</v>
+      </c>
+      <c r="G91" s="8">
+        <v>8</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S91" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F92" s="8">
+        <v>8</v>
+      </c>
+      <c r="G92" s="8">
+        <v>8</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S92" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F93" s="8">
+        <v>8</v>
+      </c>
+      <c r="G93" s="8">
+        <v>8</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S93" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F94" s="8">
+        <v>8</v>
+      </c>
+      <c r="G94" s="8">
+        <v>8</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S94" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F95" s="8">
+        <v>8</v>
+      </c>
+      <c r="G95" s="8">
+        <v>8</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S95" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96" ht="23" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F96" s="8">
+        <v>8</v>
+      </c>
+      <c r="G96" s="8">
+        <v>8</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S96" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="97" ht="23" customHeight="1">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F97" s="8">
+        <v>-9</v>
+      </c>
+      <c r="G97" s="8">
+        <v>8</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S97" s="9">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S98" s="13">
+        <f>SUM(S6:S97)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$105</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em domingo, 17 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 18 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -136,12 +136,6 @@
     <t>AZ EMPREENDIMENTOS</t>
   </si>
   <si>
-    <t>FA-11253</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>FA-11387</t>
   </si>
   <si>
@@ -157,309 +151,357 @@
     <t>NOTA DE DÉBITO</t>
   </si>
   <si>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
     <t>FA-11390</t>
   </si>
   <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>ND-11574</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
     <t>FA-11458</t>
   </si>
   <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
+    <t>FA-11615</t>
   </si>
   <si>
     <t>FA-11396</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11654</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
+  </si>
+  <si>
+    <t>FA-11642</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11466</t>
   </si>
   <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11535</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>FA-11600</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11630</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11590</t>
+  </si>
+  <si>
+    <t>FA-11577</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
   </si>
   <si>
     <t>A VENCER</t>
   </si>
   <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
     <t>FA-11480</t>
   </si>
   <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
     <t>FA-11487</t>
   </si>
   <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
     <t>FA-11563</t>
   </si>
   <si>
@@ -469,34 +511,55 @@
     <t>FA-11617</t>
   </si>
   <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11656</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
     <t>FA-11621</t>
   </si>
   <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
     <t>FA-11434</t>
   </si>
   <si>
     <t>FA-11412</t>
   </si>
   <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
     <t>FA-11489</t>
   </si>
   <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
     <t>FA-11329</t>
+  </si>
+  <si>
+    <t>FA-11536</t>
+  </si>
+  <si>
+    <t>FA-11601</t>
+  </si>
+  <si>
+    <t>FA-11578</t>
+  </si>
+  <si>
+    <t>FA-11644</t>
+  </si>
+  <si>
+    <t>FA-11591</t>
+  </si>
+  <si>
+    <t>FA-11632</t>
   </si>
   <si>
     <t>FA-11613</t>
@@ -648,7 +711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -662,7 +725,7 @@
     <col min="9" max="9" width="36.28671646118164" customWidth="1" style="1"/>
     <col min="10" max="10" width="25.261001586914062" customWidth="1" style="1"/>
     <col min="11" max="11" width="15.191652297973633" customWidth="1" style="1"/>
-    <col min="12" max="12" width="45.98413848876953" customWidth="1" style="1"/>
+    <col min="12" max="12" width="43.70395278930664" customWidth="1" style="1"/>
     <col min="13" max="13" width="38.53249740600586" customWidth="1" style="1"/>
     <col min="14" max="14" width="31.09708023071289" customWidth="1" style="1"/>
     <col min="15" max="15" width="24.68001365661621" customWidth="1" style="1"/>
@@ -765,10 +828,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="G6" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -824,10 +887,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="G7" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -874,19 +937,19 @@
         <v>46136</v>
       </c>
       <c r="C8" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="D8" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-48</v>
+        <v>-35</v>
       </c>
       <c r="G8" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -922,7 +985,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="9">
-        <v>180</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
@@ -930,25 +993,25 @@
         <v>22</v>
       </c>
       <c r="B9" s="7">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C9" s="7">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="D9" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>23</v>
+        <v>46139</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46127</v>
       </c>
       <c r="F9" s="8">
-        <v>-34</v>
+        <v>-21</v>
       </c>
       <c r="G9" s="8">
-        <v>-23</v>
+        <v>-21</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>25</v>
@@ -960,7 +1023,7 @@
         <v>23</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>23</v>
@@ -972,16 +1035,16 @@
         <v>28</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S9" s="9">
-        <v>302.72</v>
+        <v>97.15</v>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
@@ -992,19 +1055,19 @@
         <v>46139</v>
       </c>
       <c r="C10" s="7">
-        <v>46139</v>
+        <v>46082</v>
       </c>
       <c r="D10" s="7">
         <v>46139</v>
       </c>
       <c r="E10" s="7">
-        <v>46127</v>
+        <v>46097</v>
       </c>
       <c r="F10" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="G10" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1013,34 +1076,34 @@
         <v>25</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S10" s="9">
-        <v>97.15</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
@@ -1048,19 +1111,19 @@
         <v>22</v>
       </c>
       <c r="B11" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C11" s="7">
         <v>46082</v>
       </c>
       <c r="D11" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E11" s="7">
-        <v>46097</v>
+        <v>46132</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-20</v>
+        <v>-28</v>
       </c>
       <c r="G11" s="8">
         <v>-20</v>
@@ -1093,51 +1156,51 @@
         <v>23</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S11" s="9">
-        <v>146.55</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C12" s="7">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="D12" s="7">
-        <v>46132</v>
+        <v>46111</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-27</v>
+        <v>-49</v>
       </c>
       <c r="G12" s="8">
         <v>-20</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>23</v>
@@ -1155,10 +1218,10 @@
         <v>23</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S12" s="9">
-        <v>500</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1169,28 +1232,28 @@
         <v>46140</v>
       </c>
       <c r="C13" s="7">
-        <v>46082</v>
+        <v>46125</v>
       </c>
       <c r="D13" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="G13" s="8">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
@@ -1217,7 +1280,7 @@
         <v>33</v>
       </c>
       <c r="S13" s="9">
-        <v>104.04</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1225,25 +1288,25 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C14" s="7">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="D14" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E14" s="7">
+        <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-34</v>
+        <v>-10</v>
       </c>
       <c r="G14" s="8">
-        <v>-19</v>
+        <v>-14</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>25</v>
@@ -1255,7 +1318,7 @@
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>23</v>
@@ -1270,13 +1333,13 @@
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="S14" s="9">
-        <v>408.24</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1284,22 +1347,22 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="C15" s="7">
-        <v>45930</v>
+        <v>46132</v>
       </c>
       <c r="D15" s="7">
-        <v>46142</v>
+        <v>46132</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-17</v>
+        <v>-28</v>
       </c>
       <c r="G15" s="8">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1308,16 +1371,16 @@
         <v>25</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>28</v>
@@ -1332,10 +1395,10 @@
         <v>23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S15" s="9">
-        <v>185.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1346,19 +1409,19 @@
         <v>46146</v>
       </c>
       <c r="C16" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D16" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46141</v>
+        <v>46153</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="G16" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1367,16 +1430,16 @@
         <v>25</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>28</v>
@@ -1388,13 +1451,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="S16" s="9">
-        <v>12.9</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1405,19 +1468,19 @@
         <v>46146</v>
       </c>
       <c r="C17" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D17" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-27</v>
+        <v>-14</v>
       </c>
       <c r="G17" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1426,16 +1489,16 @@
         <v>25</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>28</v>
@@ -1450,10 +1513,10 @@
         <v>23</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S17" s="9">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1464,19 +1527,19 @@
         <v>46146</v>
       </c>
       <c r="C18" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D18" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46097</v>
       </c>
       <c r="F18" s="8">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G18" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -1485,16 +1548,16 @@
         <v>25</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>28</v>
@@ -1506,13 +1569,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S18" s="9">
-        <v>61.21</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1523,34 +1586,34 @@
         <v>46146</v>
       </c>
       <c r="C19" s="7">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="D19" s="7">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-34</v>
+        <v>-21</v>
       </c>
       <c r="G19" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>23</v>
@@ -1562,7 +1625,7 @@
         <v>28</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>23</v>
@@ -1571,7 +1634,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="9">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1582,19 +1645,19 @@
         <v>46146</v>
       </c>
       <c r="C20" s="7">
-        <v>46082</v>
+        <v>46146</v>
       </c>
       <c r="D20" s="7">
         <v>46146</v>
       </c>
-      <c r="E20" s="7">
-        <v>46097</v>
+      <c r="E20" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G20" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>25</v>
@@ -1603,13 +1666,13 @@
         <v>25</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1624,13 +1687,13 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S20" s="9">
-        <v>146.55</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1641,19 +1704,19 @@
         <v>46146</v>
       </c>
       <c r="C21" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D21" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46119</v>
       </c>
       <c r="F21" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1662,16 +1725,16 @@
         <v>25</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N21" s="6" t="s">
         <v>28</v>
@@ -1680,16 +1743,16 @@
         <v>28</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S21" s="9">
-        <v>150</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1700,19 +1763,19 @@
         <v>46146</v>
       </c>
       <c r="C22" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D22" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46141</v>
       </c>
       <c r="F22" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G22" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1730,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>28</v>
@@ -1742,13 +1805,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S22" s="9">
-        <v>204.67</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1759,19 +1822,19 @@
         <v>46146</v>
       </c>
       <c r="C23" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D23" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-13</v>
+        <v>-28</v>
       </c>
       <c r="G23" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1807,7 +1870,7 @@
         <v>30</v>
       </c>
       <c r="S23" s="9">
-        <v>205.82</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1818,19 +1881,19 @@
         <v>46146</v>
       </c>
       <c r="C24" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D24" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E24" s="7">
+        <v>46119</v>
       </c>
       <c r="F24" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G24" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1845,10 +1908,10 @@
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>28</v>
@@ -1857,16 +1920,16 @@
         <v>28</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S24" s="9">
-        <v>350</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1874,19 +1937,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C25" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D25" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-13</v>
+        <v>-21</v>
       </c>
       <c r="G25" s="8">
         <v>-13</v>
@@ -1904,10 +1967,10 @@
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>28</v>
@@ -1919,13 +1982,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S25" s="9">
-        <v>600</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1933,22 +1996,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C26" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D26" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="E26" s="7">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="F26" s="8">
-        <v>-13</v>
+        <v>-18</v>
       </c>
       <c r="G26" s="8">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -1957,13 +2020,13 @@
         <v>25</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1978,13 +2041,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="S26" s="9">
-        <v>620</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1992,37 +2055,37 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C27" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D27" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46112</v>
+        <v>46125</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-13</v>
+        <v>-35</v>
       </c>
       <c r="G27" s="8">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2037,13 +2100,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S27" s="9">
-        <v>630</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2051,7 +2114,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C28" s="7">
         <v>46146</v>
@@ -2059,14 +2122,14 @@
       <c r="D28" s="7">
         <v>46146</v>
       </c>
-      <c r="E28" s="7">
-        <v>46119</v>
+      <c r="E28" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G28" s="8">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2075,16 +2138,16 @@
         <v>25</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>28</v>
@@ -2096,13 +2159,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S28" s="9">
-        <v>650</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2110,22 +2173,22 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C29" s="7">
-        <v>46132</v>
+        <v>46150</v>
       </c>
       <c r="D29" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46153</v>
       </c>
       <c r="F29" s="8">
-        <v>-27</v>
+        <v>-10</v>
       </c>
       <c r="G29" s="8">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2134,13 +2197,13 @@
         <v>25</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2155,13 +2218,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S29" s="9">
-        <v>655.21</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2169,37 +2232,37 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C30" s="7">
-        <v>46146</v>
+        <v>45901</v>
       </c>
       <c r="D30" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E30" s="7">
-        <v>46119</v>
+        <v>45938</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-13</v>
+        <v>-222</v>
       </c>
       <c r="G30" s="8">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2211,16 +2274,16 @@
         <v>28</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S30" s="9">
-        <v>700</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2228,22 +2291,22 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="C31" s="7">
-        <v>46139</v>
+        <v>46082</v>
       </c>
       <c r="D31" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46097</v>
       </c>
       <c r="F31" s="8">
-        <v>-20</v>
+        <v>-7</v>
       </c>
       <c r="G31" s="8">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2252,13 +2315,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2273,13 +2336,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S31" s="9">
-        <v>103.36</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2287,22 +2350,22 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="C32" s="7">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="D32" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E32" s="7">
-        <v>46148</v>
+        <v>46132</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-17</v>
+        <v>-28</v>
       </c>
       <c r="G32" s="8">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2311,13 +2374,13 @@
         <v>25</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2332,13 +2395,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="S32" s="9">
-        <v>685.71</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2346,40 +2409,40 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C33" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="D33" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E33" s="7">
+        <v>46127</v>
       </c>
       <c r="F33" s="8">
-        <v>-34</v>
+        <v>-7</v>
       </c>
       <c r="G33" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>28</v>
@@ -2391,13 +2454,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S33" s="9">
-        <v>53.82</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2405,22 +2468,22 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C34" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D34" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="G34" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2429,16 +2492,16 @@
         <v>25</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>28</v>
@@ -2450,13 +2513,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S34" s="9">
-        <v>170</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2464,22 +2527,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C35" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D35" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="7">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="F35" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="G35" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2488,13 +2551,13 @@
         <v>25</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2509,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S35" s="9">
-        <v>278.57</v>
+        <v>620</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2526,37 +2589,37 @@
         <v>46153</v>
       </c>
       <c r="C36" s="7">
-        <v>45901</v>
+        <v>46153</v>
       </c>
       <c r="D36" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46141</v>
       </c>
       <c r="F36" s="8">
-        <v>-221</v>
+        <v>-7</v>
       </c>
       <c r="G36" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I36" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="6" t="s">
+      <c r="K36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>28</v>
@@ -2568,13 +2631,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S36" s="9">
-        <v>30</v>
+        <v>620</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2585,19 +2648,19 @@
         <v>46153</v>
       </c>
       <c r="C37" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D37" s="7">
         <v>46153</v>
       </c>
       <c r="E37" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F37" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G37" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>25</v>
@@ -2606,16 +2669,16 @@
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>28</v>
@@ -2627,13 +2690,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S37" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2644,19 +2707,19 @@
         <v>46153</v>
       </c>
       <c r="C38" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="D38" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46112</v>
       </c>
       <c r="F38" s="8">
-        <v>-27</v>
+        <v>-7</v>
       </c>
       <c r="G38" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>25</v>
@@ -2665,13 +2728,13 @@
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2686,13 +2749,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S38" s="9">
-        <v>450</v>
+        <v>630</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2712,10 +2775,10 @@
         <v>46119</v>
       </c>
       <c r="F39" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G39" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2724,16 +2787,16 @@
         <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>28</v>
@@ -2745,13 +2808,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S39" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2768,13 +2831,13 @@
         <v>46153</v>
       </c>
       <c r="E40" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F40" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G40" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -2783,16 +2846,16 @@
         <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>28</v>
@@ -2804,13 +2867,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S40" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2827,13 +2890,13 @@
         <v>46153</v>
       </c>
       <c r="E41" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F41" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G41" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -2842,13 +2905,13 @@
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2863,13 +2926,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S41" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2889,10 +2952,10 @@
         <v>46141</v>
       </c>
       <c r="F42" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G42" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2901,16 +2964,16 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>28</v>
@@ -2922,13 +2985,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S42" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2948,10 +3011,10 @@
         <v>46119</v>
       </c>
       <c r="F43" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G43" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -2960,16 +3023,16 @@
         <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>28</v>
@@ -2981,13 +3044,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S43" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -3004,13 +3067,13 @@
         <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F44" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G44" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>25</v>
@@ -3019,13 +3082,13 @@
         <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -3037,16 +3100,16 @@
         <v>28</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S44" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3054,37 +3117,37 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C45" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="D45" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E45" s="7">
-        <v>46150</v>
+        <v>46125</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>-6</v>
+        <v>-35</v>
       </c>
       <c r="G45" s="8">
         <v>-6</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3099,13 +3162,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S45" s="9">
-        <v>630</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3113,19 +3176,19 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C46" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D46" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E46" s="7">
-        <v>46092</v>
+        <v>46146</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F46" s="8">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G46" s="8">
         <v>-6</v>
@@ -3137,13 +3200,13 @@
         <v>25</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3158,13 +3221,13 @@
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S46" s="9">
-        <v>650</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3172,19 +3235,19 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C47" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D47" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E47" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-6</v>
+        <v>-28</v>
       </c>
       <c r="G47" s="8">
         <v>-6</v>
@@ -3196,16 +3259,16 @@
         <v>25</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>28</v>
@@ -3217,13 +3280,13 @@
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S47" s="9">
-        <v>650</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3231,22 +3294,22 @@
         <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C48" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D48" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E48" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>-6</v>
+        <v>-28</v>
       </c>
       <c r="G48" s="8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>25</v>
@@ -3255,13 +3318,13 @@
         <v>25</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3276,13 +3339,13 @@
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S48" s="9">
-        <v>680</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3290,22 +3353,22 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C49" s="7">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="D49" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E49" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>-6</v>
+        <v>-21</v>
       </c>
       <c r="G49" s="8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>25</v>
@@ -3320,10 +3383,10 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>28</v>
@@ -3335,13 +3398,13 @@
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S49" s="9">
-        <v>680</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3349,7 +3412,7 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C50" s="7">
         <v>46153</v>
@@ -3357,14 +3420,14 @@
       <c r="D50" s="7">
         <v>46153</v>
       </c>
-      <c r="E50" s="7">
-        <v>46141</v>
+      <c r="E50" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F50" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G50" s="8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>25</v>
@@ -3379,7 +3442,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3394,13 +3457,13 @@
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S50" s="9">
-        <v>680</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3408,22 +3471,22 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="C51" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D51" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E51" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F51" s="8">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G51" s="8">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3432,13 +3495,13 @@
         <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3450,16 +3513,16 @@
         <v>28</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S51" s="9">
-        <v>700</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3467,46 +3530,46 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C52" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="D52" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="G52" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
@@ -3515,10 +3578,10 @@
         <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S52" s="9">
-        <v>150</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3526,58 +3589,58 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C53" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D53" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46097</v>
       </c>
       <c r="F53" s="8">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="G53" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S53" s="9">
-        <v>280</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3585,117 +3648,117 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C54" s="7">
-        <v>46132</v>
+        <v>46157</v>
       </c>
       <c r="D54" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>23</v>
+        <v>46157</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46160</v>
       </c>
       <c r="F54" s="8">
-        <v>-27</v>
+        <v>-3</v>
       </c>
       <c r="G54" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S54" s="9">
-        <v>317.54</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B55" s="7">
         <v>46160</v>
       </c>
       <c r="C55" s="7">
-        <v>46082</v>
+        <v>46158</v>
       </c>
       <c r="D55" s="7">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="E55" s="7">
-        <v>46097</v>
+        <v>46160</v>
       </c>
       <c r="F55" s="8">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G55" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="S55" s="9">
-        <v>146.55</v>
+        <v>342.86</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3706,55 +3769,55 @@
         <v>46160</v>
       </c>
       <c r="C56" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D56" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46112</v>
+        <v>46146</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="G56" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S56" s="9">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3771,13 +3834,13 @@
         <v>46160</v>
       </c>
       <c r="E57" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F57" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3786,28 +3849,28 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>30</v>
@@ -3833,10 +3896,10 @@
         <v>46127</v>
       </c>
       <c r="F58" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3845,28 +3908,28 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>30</v>
@@ -3889,13 +3952,13 @@
         <v>46160</v>
       </c>
       <c r="E59" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3904,34 +3967,34 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S59" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3951,10 +4014,10 @@
         <v>46141</v>
       </c>
       <c r="F60" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -3963,28 +4026,28 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>30</v>
@@ -4010,10 +4073,10 @@
         <v>46119</v>
       </c>
       <c r="F61" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -4022,28 +4085,28 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>33</v>
@@ -4066,13 +4129,13 @@
         <v>46160</v>
       </c>
       <c r="E62" s="7">
-        <v>46112</v>
+        <v>46141</v>
       </c>
       <c r="F62" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4081,34 +4144,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S62" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4128,10 +4191,10 @@
         <v>46112</v>
       </c>
       <c r="F63" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4140,28 +4203,28 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>30</v>
@@ -4184,13 +4247,13 @@
         <v>46160</v>
       </c>
       <c r="E64" s="7">
-        <v>46127</v>
+        <v>46112</v>
       </c>
       <c r="F64" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4199,28 +4262,28 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>30</v>
@@ -4243,13 +4306,13 @@
         <v>46160</v>
       </c>
       <c r="E65" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F65" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4258,28 +4321,28 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>30</v>
@@ -4305,10 +4368,10 @@
         <v>46150</v>
       </c>
       <c r="F66" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4317,28 +4380,28 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>30</v>
@@ -4361,13 +4424,13 @@
         <v>46160</v>
       </c>
       <c r="E67" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4376,34 +4439,34 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S67" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4420,13 +4483,13 @@
         <v>46160</v>
       </c>
       <c r="E68" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F68" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4435,28 +4498,28 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>30</v>
@@ -4479,13 +4542,13 @@
         <v>46160</v>
       </c>
       <c r="E69" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F69" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4494,28 +4557,28 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>30</v>
@@ -4538,13 +4601,13 @@
         <v>46160</v>
       </c>
       <c r="E70" s="7">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="F70" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4553,28 +4616,28 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>30</v>
@@ -4597,13 +4660,13 @@
         <v>46160</v>
       </c>
       <c r="E71" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F71" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4612,34 +4675,34 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S71" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4656,13 +4719,13 @@
         <v>46160</v>
       </c>
       <c r="E72" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4671,34 +4734,34 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S72" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4715,13 +4778,13 @@
         <v>46160</v>
       </c>
       <c r="E73" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F73" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4730,28 +4793,28 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>30</v>
@@ -4777,10 +4840,10 @@
         <v>46119</v>
       </c>
       <c r="F74" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4789,7 +4852,7 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
@@ -4801,16 +4864,16 @@
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>33</v>
@@ -4836,10 +4899,10 @@
         <v>46141</v>
       </c>
       <c r="F75" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4848,28 +4911,28 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>33</v>
@@ -4895,10 +4958,10 @@
         <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4907,34 +4970,34 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S76" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -4951,13 +5014,13 @@
         <v>46160</v>
       </c>
       <c r="E77" s="7">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="F77" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4966,31 +5029,31 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S77" s="9">
         <v>700</v>
@@ -5010,13 +5073,13 @@
         <v>46160</v>
       </c>
       <c r="E78" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F78" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5025,28 +5088,28 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>30</v>
@@ -5060,81 +5123,81 @@
         <v>22</v>
       </c>
       <c r="B79" s="7">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="C79" s="7">
-        <v>46113</v>
+        <v>46160</v>
       </c>
       <c r="D79" s="7">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="E79" s="7">
-        <v>46149</v>
+        <v>46099</v>
       </c>
       <c r="F79" s="8">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G79" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S79" s="9">
-        <v>2100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80" ht="23" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="B80" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C80" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D80" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E80" s="7">
-        <v>46097</v>
+        <v>46129</v>
       </c>
       <c r="F80" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5143,57 +5206,57 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="S80" s="9">
-        <v>146.55</v>
+        <v>800</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="B81" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C81" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D81" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E81" s="7">
-        <v>46119</v>
+        <v>46148</v>
       </c>
       <c r="F81" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G81" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5202,34 +5265,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="S81" s="9">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="82" ht="23" customHeight="1">
@@ -5237,81 +5300,81 @@
         <v>22</v>
       </c>
       <c r="B82" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C82" s="7">
-        <v>46167</v>
+        <v>46154</v>
       </c>
       <c r="D82" s="7">
-        <v>46167</v>
+        <v>46154</v>
       </c>
       <c r="E82" s="7">
-        <v>46119</v>
+        <v>46160</v>
       </c>
       <c r="F82" s="8">
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="G82" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="S82" s="9">
-        <v>620</v>
+        <v>1028.57</v>
       </c>
     </row>
     <row r="83" ht="23" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B83" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C83" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D83" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E83" s="7">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="F83" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G83" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5320,57 +5383,57 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="S83" s="9">
-        <v>620</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="84" ht="23" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B84" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C84" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D84" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E84" s="7">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="F84" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5379,34 +5442,34 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="S84" s="9">
-        <v>620</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="85" ht="23" customHeight="1">
@@ -5414,58 +5477,58 @@
         <v>22</v>
       </c>
       <c r="B85" s="7">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="C85" s="7">
-        <v>46167</v>
+        <v>46113</v>
       </c>
       <c r="D85" s="7">
-        <v>46167</v>
+        <v>46150</v>
       </c>
       <c r="E85" s="7">
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="F85" s="8">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="G85" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S85" s="9">
-        <v>630</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="86" ht="23" customHeight="1">
@@ -5476,19 +5539,19 @@
         <v>46167</v>
       </c>
       <c r="C86" s="7">
-        <v>46167</v>
+        <v>46082</v>
       </c>
       <c r="D86" s="7">
         <v>46167</v>
       </c>
       <c r="E86" s="7">
-        <v>46150</v>
+        <v>46097</v>
       </c>
       <c r="F86" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G86" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5497,34 +5560,34 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S86" s="9">
-        <v>630</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="87" ht="23" customHeight="1">
@@ -5541,13 +5604,13 @@
         <v>46167</v>
       </c>
       <c r="E87" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F87" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G87" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5556,34 +5619,34 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S87" s="9">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" ht="23" customHeight="1">
@@ -5600,13 +5663,13 @@
         <v>46167</v>
       </c>
       <c r="E88" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F88" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G88" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5615,34 +5678,34 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q88" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S88" s="9">
-        <v>650</v>
+        <v>620</v>
       </c>
     </row>
     <row r="89" ht="23" customHeight="1">
@@ -5662,10 +5725,10 @@
         <v>46119</v>
       </c>
       <c r="F89" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G89" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5674,34 +5737,34 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q89" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S89" s="9">
-        <v>650</v>
+        <v>620</v>
       </c>
     </row>
     <row r="90" ht="23" customHeight="1">
@@ -5718,13 +5781,13 @@
         <v>46167</v>
       </c>
       <c r="E90" s="7">
-        <v>46092</v>
+        <v>46141</v>
       </c>
       <c r="F90" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G90" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5733,34 +5796,34 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q90" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S90" s="9">
-        <v>650</v>
+        <v>620</v>
       </c>
     </row>
     <row r="91" ht="23" customHeight="1">
@@ -5780,10 +5843,10 @@
         <v>46119</v>
       </c>
       <c r="F91" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G91" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5792,34 +5855,34 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q91" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S91" s="9">
-        <v>670</v>
+        <v>630</v>
       </c>
     </row>
     <row r="92" ht="23" customHeight="1">
@@ -5836,13 +5899,13 @@
         <v>46167</v>
       </c>
       <c r="E92" s="7">
-        <v>46113</v>
+        <v>46150</v>
       </c>
       <c r="F92" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G92" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5851,34 +5914,34 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q92" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S92" s="9">
-        <v>680</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93" ht="23" customHeight="1">
@@ -5895,13 +5958,13 @@
         <v>46167</v>
       </c>
       <c r="E93" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F93" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G93" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5910,34 +5973,34 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q93" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S93" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="94" ht="23" customHeight="1">
@@ -5957,10 +6020,10 @@
         <v>46119</v>
       </c>
       <c r="F94" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G94" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -5969,34 +6032,34 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N94" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="O94" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q94" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S94" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="95" ht="23" customHeight="1">
@@ -6013,13 +6076,13 @@
         <v>46167</v>
       </c>
       <c r="E95" s="7">
-        <v>46141</v>
+        <v>46160</v>
       </c>
       <c r="F95" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G95" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6028,34 +6091,34 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S95" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="96" ht="23" customHeight="1">
@@ -6072,13 +6135,13 @@
         <v>46167</v>
       </c>
       <c r="E96" s="7">
-        <v>46099</v>
+        <v>46127</v>
       </c>
       <c r="F96" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G96" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6087,34 +6150,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S96" s="9">
-        <v>700</v>
+        <v>650</v>
       </c>
     </row>
     <row r="97" ht="23" customHeight="1">
@@ -6125,114 +6188,881 @@
         <v>46167</v>
       </c>
       <c r="C97" s="7">
-        <v>46113</v>
+        <v>46167</v>
       </c>
       <c r="D97" s="7">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="E97" s="7">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="F97" s="8">
-        <v>-9</v>
+        <v>7</v>
       </c>
       <c r="G97" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S97" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F98" s="8">
+        <v>7</v>
+      </c>
+      <c r="G98" s="8">
+        <v>7</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S98" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C99" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D99" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F99" s="8">
+        <v>7</v>
+      </c>
+      <c r="G99" s="8">
+        <v>7</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S99" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="100" ht="23" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C100" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D100" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E100" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F100" s="8">
+        <v>7</v>
+      </c>
+      <c r="G100" s="8">
+        <v>7</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S100" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C101" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D101" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E101" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F101" s="8">
+        <v>7</v>
+      </c>
+      <c r="G101" s="8">
+        <v>7</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S101" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="102" ht="23" customHeight="1">
+      <c r="A102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C102" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D102" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E102" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F102" s="8">
+        <v>7</v>
+      </c>
+      <c r="G102" s="8">
+        <v>7</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S102" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="103" ht="23" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C103" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D103" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E103" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F103" s="8">
+        <v>7</v>
+      </c>
+      <c r="G103" s="8">
+        <v>7</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S103" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="104" ht="23" customHeight="1">
+      <c r="A104" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B104" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C104" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D104" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E104" s="7">
+        <v>46129</v>
+      </c>
+      <c r="F104" s="8">
+        <v>7</v>
+      </c>
+      <c r="G104" s="8">
+        <v>7</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S104" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="105" ht="23" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C105" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D105" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E105" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F105" s="8">
+        <v>7</v>
+      </c>
+      <c r="G105" s="8">
+        <v>7</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S105" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="106" ht="23" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C106" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D106" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E106" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F106" s="8">
+        <v>7</v>
+      </c>
+      <c r="G106" s="8">
+        <v>7</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q106" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S106" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C107" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D107" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E107" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F107" s="8">
+        <v>7</v>
+      </c>
+      <c r="G107" s="8">
+        <v>7</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N107" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O107" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q107" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S107" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="108" ht="23" customHeight="1">
+      <c r="A108" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B108" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C108" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D108" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E108" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F108" s="8">
+        <v>7</v>
+      </c>
+      <c r="G108" s="8">
+        <v>7</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q108" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S108" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="109" ht="23" customHeight="1">
+      <c r="A109" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C109" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D109" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E109" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F109" s="8">
+        <v>7</v>
+      </c>
+      <c r="G109" s="8">
+        <v>7</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="K109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N109" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O109" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S109" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="110" ht="23" customHeight="1">
+      <c r="A110" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C110" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D110" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E110" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F110" s="8">
+        <v>-10</v>
+      </c>
+      <c r="G110" s="8">
+        <v>7</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q110" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S110" s="9">
         <v>4400</v>
       </c>
     </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F98" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R98" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S98" s="13">
-        <f>SUM(S6:S97)</f>
+    <row r="111" ht="23" customHeight="1">
+      <c r="A111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S111" s="13">
+        <f>SUM(S6:S110)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -310,57 +310,57 @@
     <t>FA-11616</t>
   </si>
   <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
     <t>FA-11667</t>
   </si>
   <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
     <t>A VENCER</t>
   </si>
   <si>
@@ -388,13 +388,13 @@
     <t>FA-11668</t>
   </si>
   <si>
+    <t>FA-11656</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
     <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11656</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
   </si>
   <si>
     <t>FA-11504</t>
@@ -3307,7 +3307,7 @@
         <v>46160</v>
       </c>
       <c r="E50" s="7">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="F50" s="8">
         <v>-3</v>
@@ -3328,7 +3328,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3349,7 +3349,7 @@
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3366,7 +3366,7 @@
         <v>46160</v>
       </c>
       <c r="E51" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F51" s="8">
         <v>-3</v>
@@ -3387,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
@@ -3446,10 +3446,10 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3467,7 +3467,7 @@
         <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3499,13 +3499,13 @@
         <v>30</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3523,7 +3523,7 @@
         <v>37</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S53" s="9">
         <v>680</v>
@@ -3543,7 +3543,7 @@
         <v>46160</v>
       </c>
       <c r="E54" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
         <v>-3</v>
@@ -3564,7 +3564,7 @@
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3602,7 +3602,7 @@
         <v>46160</v>
       </c>
       <c r="E55" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F55" s="8">
         <v>-3</v>
@@ -3617,13 +3617,13 @@
         <v>30</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3635,16 +3635,16 @@
         <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3652,22 +3652,22 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C56" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D56" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-3</v>
+        <v>-24</v>
       </c>
       <c r="G56" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>30</v>
@@ -3676,13 +3676,13 @@
         <v>30</v>
       </c>
       <c r="J56" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3697,13 +3697,13 @@
         <v>28</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3714,16 +3714,16 @@
         <v>46161</v>
       </c>
       <c r="C57" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D57" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>-24</v>
+        <v>-3</v>
       </c>
       <c r="G57" s="8">
         <v>-2</v>
@@ -3741,7 +3741,7 @@
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
@@ -3753,7 +3753,7 @@
         <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3762,7 +3762,7 @@
         <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>50</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3773,16 +3773,16 @@
         <v>46161</v>
       </c>
       <c r="C58" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D58" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G58" s="8">
         <v>-2</v>
@@ -3794,16 +3794,16 @@
         <v>30</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3818,10 +3818,10 @@
         <v>23</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S58" s="9">
-        <v>130</v>
+        <v>277.36</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3832,16 +3832,16 @@
         <v>46161</v>
       </c>
       <c r="C59" s="7">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="D59" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46149</v>
       </c>
       <c r="F59" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="G59" s="8">
         <v>-2</v>
@@ -3859,10 +3859,10 @@
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3874,13 +3874,13 @@
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>277.36</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3888,22 +3888,22 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C60" s="7">
-        <v>46113</v>
+        <v>46146</v>
       </c>
       <c r="D60" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46149</v>
+        <v>46146</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F60" s="8">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="G60" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>30</v>
@@ -3912,16 +3912,16 @@
         <v>30</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>27</v>
@@ -3933,13 +3933,13 @@
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>2100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3947,28 +3947,28 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C61" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D61" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G61" s="8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>108</v>
@@ -3977,16 +3977,16 @@
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -3998,7 +3998,7 @@
         <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>200</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4487,7 +4487,7 @@
         <v>46167</v>
       </c>
       <c r="E70" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="F70" s="8">
         <v>4</v>
@@ -4508,7 +4508,7 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
@@ -4546,7 +4546,7 @@
         <v>46167</v>
       </c>
       <c r="E71" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="F71" s="8">
         <v>4</v>
@@ -4561,13 +4561,13 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
@@ -4744,7 +4744,7 @@
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
@@ -4921,7 +4921,7 @@
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
@@ -5039,7 +5039,7 @@
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$82</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 21 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sexta-feira, 22 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -235,132 +235,144 @@
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11675</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11674</t>
+  </si>
+  <si>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11667</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
     <t>FA-11399</t>
   </si>
   <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11667</t>
-  </si>
-  <si>
     <t>A VENCER</t>
   </si>
   <si>
@@ -388,6 +400,12 @@
     <t>FA-11668</t>
   </si>
   <si>
+    <t>FA-11683</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
     <t>FA-11656</t>
   </si>
   <si>
@@ -427,25 +445,28 @@
     <t>FA-11564</t>
   </si>
   <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
     <t>FA-11329</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
+    <t>FA-11632</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11644</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11632</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
   </si>
   <si>
     <t>FA-11613</t>
@@ -597,7 +618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -714,10 +735,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="G6" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -773,10 +794,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G7" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -832,10 +853,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G8" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -891,10 +912,10 @@
         <v>46127</v>
       </c>
       <c r="F9" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G9" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>30</v>
@@ -950,10 +971,10 @@
         <v>46097</v>
       </c>
       <c r="F10" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G10" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>30</v>
@@ -1009,10 +1030,10 @@
         <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G11" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1068,10 +1089,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G12" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1127,10 +1148,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G13" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>30</v>
@@ -1186,10 +1207,10 @@
         <v>23</v>
       </c>
       <c r="F14" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G14" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>30</v>
@@ -1245,10 +1266,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>30</v>
@@ -1304,10 +1325,10 @@
         <v>46097</v>
       </c>
       <c r="F16" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G16" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>30</v>
@@ -1363,10 +1384,10 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G17" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>30</v>
@@ -1422,10 +1443,10 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G18" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>30</v>
@@ -1481,10 +1502,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G19" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>24</v>
@@ -1540,10 +1561,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G20" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>30</v>
@@ -1599,10 +1620,10 @@
         <v>46148</v>
       </c>
       <c r="F21" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G21" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>30</v>
@@ -1658,10 +1679,10 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G22" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>24</v>
@@ -1717,10 +1738,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G23" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>30</v>
@@ -1776,10 +1797,10 @@
         <v>46153</v>
       </c>
       <c r="F24" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G24" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>30</v>
@@ -1835,10 +1856,10 @@
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-225</v>
+        <v>-226</v>
       </c>
       <c r="G25" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>62</v>
@@ -1894,10 +1915,10 @@
         <v>46097</v>
       </c>
       <c r="F26" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G26" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>30</v>
@@ -1953,10 +1974,10 @@
         <v>46141</v>
       </c>
       <c r="F27" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G27" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>30</v>
@@ -2012,10 +2033,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G28" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>30</v>
@@ -2068,13 +2089,13 @@
         <v>46153</v>
       </c>
       <c r="E29" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F29" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G29" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>30</v>
@@ -2089,10 +2110,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2110,7 +2131,7 @@
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2130,10 +2151,10 @@
         <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G30" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>30</v>
@@ -2142,16 +2163,16 @@
         <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2166,10 +2187,10 @@
         <v>37</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S30" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2177,19 +2198,19 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C31" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D31" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="G31" s="8">
         <v>-10</v>
@@ -2207,7 +2228,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2222,13 +2243,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2239,19 +2260,19 @@
         <v>46154</v>
       </c>
       <c r="C32" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D32" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-38</v>
+        <v>-32</v>
       </c>
       <c r="G32" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>24</v>
@@ -2260,16 +2281,16 @@
         <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2284,10 +2305,10 @@
         <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>150</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2295,25 +2316,25 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C33" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D33" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-17</v>
+        <v>-32</v>
       </c>
       <c r="G33" s="8">
         <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>30</v>
@@ -2325,7 +2346,7 @@
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2346,7 +2367,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>280</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2354,40 +2375,40 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C34" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D34" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-31</v>
+        <v>-25</v>
       </c>
       <c r="G34" s="8">
         <v>-9</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2405,7 +2426,7 @@
         <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>317.54</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2416,34 +2437,34 @@
         <v>46155</v>
       </c>
       <c r="C35" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-31</v>
+        <v>-11</v>
       </c>
       <c r="G35" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2464,7 +2485,7 @@
         <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>140</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2472,19 +2493,19 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C36" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D36" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="G36" s="8">
         <v>-8</v>
@@ -2496,16 +2517,16 @@
         <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2523,7 +2544,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>250</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2531,22 +2552,22 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C37" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D37" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G37" s="8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>30</v>
@@ -2555,13 +2576,13 @@
         <v>30</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2582,7 +2603,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>530</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2590,22 +2611,22 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="C38" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D38" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46097</v>
       </c>
       <c r="F38" s="8">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G38" s="8">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>30</v>
@@ -2614,13 +2635,13 @@
         <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2635,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S38" s="9">
-        <v>130</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2657,14 +2678,14 @@
       <c r="D39" s="7">
         <v>46160</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+      <c r="E39" s="7">
+        <v>46127</v>
       </c>
       <c r="F39" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>30</v>
@@ -2673,16 +2694,16 @@
         <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2694,13 +2715,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>97.5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2711,19 +2732,19 @@
         <v>46160</v>
       </c>
       <c r="C40" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D40" s="7">
         <v>46160</v>
       </c>
       <c r="E40" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>30</v>
@@ -2732,13 +2753,13 @@
         <v>30</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2753,13 +2774,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2770,22 +2791,22 @@
         <v>46160</v>
       </c>
       <c r="C41" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D41" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46127</v>
+        <v>46132</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-3</v>
+        <v>-32</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>30</v>
@@ -2800,7 +2821,7 @@
         <v>81</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2812,13 +2833,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S41" s="9">
-        <v>172</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2829,19 +2850,19 @@
         <v>46160</v>
       </c>
       <c r="C42" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D42" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E42" s="7">
-        <v>46141</v>
+        <v>46146</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>30</v>
@@ -2856,10 +2877,10 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>27</v>
@@ -2871,13 +2892,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>310</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2888,22 +2909,22 @@
         <v>46160</v>
       </c>
       <c r="C43" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D43" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46119</v>
       </c>
       <c r="F43" s="8">
-        <v>-31</v>
+        <v>-4</v>
       </c>
       <c r="G43" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>30</v>
@@ -2915,10 +2936,10 @@
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2930,13 +2951,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2947,19 +2968,19 @@
         <v>46160</v>
       </c>
       <c r="C44" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D44" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46141</v>
       </c>
       <c r="F44" s="8">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>30</v>
@@ -2974,10 +2995,10 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -2989,13 +3010,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>450</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3015,10 +3036,10 @@
         <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>30</v>
@@ -3027,16 +3048,16 @@
         <v>30</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -3051,10 +3072,10 @@
         <v>37</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S45" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3071,13 +3092,13 @@
         <v>46160</v>
       </c>
       <c r="E46" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F46" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G46" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>30</v>
@@ -3086,16 +3107,16 @@
         <v>30</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3113,7 +3134,7 @@
         <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3130,13 +3151,13 @@
         <v>46160</v>
       </c>
       <c r="E47" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F47" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G47" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>30</v>
@@ -3145,16 +3166,16 @@
         <v>30</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
@@ -3169,10 +3190,10 @@
         <v>37</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3189,13 +3210,13 @@
         <v>46160</v>
       </c>
       <c r="E48" s="7">
-        <v>46112</v>
+        <v>46153</v>
       </c>
       <c r="F48" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G48" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>30</v>
@@ -3210,7 +3231,7 @@
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3231,7 +3252,7 @@
         <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3248,13 +3269,13 @@
         <v>46160</v>
       </c>
       <c r="E49" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G49" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>30</v>
@@ -3269,10 +3290,10 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3290,7 +3311,7 @@
         <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3307,13 +3328,13 @@
         <v>46160</v>
       </c>
       <c r="E50" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F50" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G50" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>30</v>
@@ -3328,7 +3349,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3349,7 +3370,7 @@
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3369,10 +3390,10 @@
         <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G51" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>30</v>
@@ -3381,16 +3402,16 @@
         <v>30</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
@@ -3405,10 +3426,10 @@
         <v>37</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S51" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3425,13 +3446,13 @@
         <v>46160</v>
       </c>
       <c r="E52" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F52" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G52" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>30</v>
@@ -3440,13 +3461,13 @@
         <v>30</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3464,7 +3485,7 @@
         <v>37</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S52" s="9">
         <v>680</v>
@@ -3484,13 +3505,13 @@
         <v>46160</v>
       </c>
       <c r="E53" s="7">
-        <v>46119</v>
+        <v>46164</v>
       </c>
       <c r="F53" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G53" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>30</v>
@@ -3499,13 +3520,13 @@
         <v>30</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3543,13 +3564,13 @@
         <v>46160</v>
       </c>
       <c r="E54" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F54" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G54" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>30</v>
@@ -3558,13 +3579,13 @@
         <v>30</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3576,16 +3597,16 @@
         <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S54" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3593,19 +3614,19 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C55" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D55" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-3</v>
+        <v>-25</v>
       </c>
       <c r="G55" s="8">
         <v>-3</v>
@@ -3617,7 +3638,7 @@
         <v>30</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
@@ -3638,13 +3659,13 @@
         <v>28</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3655,19 +3676,19 @@
         <v>46161</v>
       </c>
       <c r="C56" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D56" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="G56" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>30</v>
@@ -3676,13 +3697,13 @@
         <v>30</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3694,7 +3715,7 @@
         <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>23</v>
@@ -3703,7 +3724,7 @@
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>50</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3714,20 +3735,20 @@
         <v>46161</v>
       </c>
       <c r="C57" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D57" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="8">
+        <v>-11</v>
+      </c>
+      <c r="G57" s="8">
         <v>-3</v>
       </c>
-      <c r="G57" s="8">
-        <v>-2</v>
-      </c>
       <c r="H57" s="6" t="s">
         <v>30</v>
       </c>
@@ -3735,16 +3756,16 @@
         <v>30</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3759,10 +3780,10 @@
         <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S57" s="9">
-        <v>130</v>
+        <v>277.36</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3782,10 +3803,10 @@
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G58" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>30</v>
@@ -3794,16 +3815,16 @@
         <v>30</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3821,7 +3842,7 @@
         <v>33</v>
       </c>
       <c r="S58" s="9">
-        <v>277.36</v>
+        <v>280</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3841,10 +3862,10 @@
         <v>46149</v>
       </c>
       <c r="F59" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G59" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>30</v>
@@ -3853,16 +3874,16 @@
         <v>30</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3891,37 +3912,37 @@
         <v>46162</v>
       </c>
       <c r="C60" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D60" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="8">
-        <v>-17</v>
+        <v>-39</v>
       </c>
       <c r="G60" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>30</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>27</v>
@@ -3936,10 +3957,10 @@
         <v>23</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S60" s="9">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3947,46 +3968,46 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="C61" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D61" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G61" s="8">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -3998,7 +4019,7 @@
         <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4006,58 +4027,58 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="C62" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D62" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E62" s="7">
-        <v>46097</v>
+        <v>46160</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F62" s="8">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="G62" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S62" s="9">
-        <v>146.55</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4068,55 +4089,55 @@
         <v>46167</v>
       </c>
       <c r="C63" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D63" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E63" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F63" s="8">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="G63" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S63" s="9">
-        <v>600</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4127,19 +4148,19 @@
         <v>46167</v>
       </c>
       <c r="C64" s="7">
-        <v>46167</v>
+        <v>46082</v>
       </c>
       <c r="D64" s="7">
         <v>46167</v>
       </c>
       <c r="E64" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F64" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4148,34 +4169,34 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S64" s="9">
-        <v>620</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4192,13 +4213,13 @@
         <v>46167</v>
       </c>
       <c r="E65" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F65" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4207,22 +4228,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4234,7 +4255,7 @@
         <v>29</v>
       </c>
       <c r="S65" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4251,13 +4272,13 @@
         <v>46167</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F66" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4266,22 +4287,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="O66" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4290,7 +4311,7 @@
         <v>37</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S66" s="9">
         <v>620</v>
@@ -4310,13 +4331,13 @@
         <v>46167</v>
       </c>
       <c r="E67" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F67" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4325,25 +4346,25 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q67" s="6" t="s">
         <v>37</v>
@@ -4352,7 +4373,7 @@
         <v>29</v>
       </c>
       <c r="S67" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4369,13 +4390,13 @@
         <v>46167</v>
       </c>
       <c r="E68" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F68" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4384,22 +4405,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4408,10 +4429,10 @@
         <v>37</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S68" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4428,13 +4449,13 @@
         <v>46167</v>
       </c>
       <c r="E69" s="7">
-        <v>46163</v>
+        <v>46119</v>
       </c>
       <c r="F69" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4443,25 +4464,25 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q69" s="6" t="s">
         <v>37</v>
@@ -4487,13 +4508,13 @@
         <v>46167</v>
       </c>
       <c r="E70" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="F70" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4502,22 +4523,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4529,7 +4550,7 @@
         <v>29</v>
       </c>
       <c r="S70" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4546,13 +4567,13 @@
         <v>46167</v>
       </c>
       <c r="E71" s="7">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="F71" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4561,22 +4582,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4588,7 +4609,7 @@
         <v>29</v>
       </c>
       <c r="S71" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4605,13 +4626,13 @@
         <v>46167</v>
       </c>
       <c r="E72" s="7">
-        <v>46127</v>
+        <v>46164</v>
       </c>
       <c r="F72" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4620,22 +4641,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4647,7 +4668,7 @@
         <v>29</v>
       </c>
       <c r="S72" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4664,13 +4685,13 @@
         <v>46167</v>
       </c>
       <c r="E73" s="7">
-        <v>46119</v>
+        <v>46160</v>
       </c>
       <c r="F73" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4679,22 +4700,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4723,13 +4744,13 @@
         <v>46167</v>
       </c>
       <c r="E74" s="7">
-        <v>46092</v>
+        <v>46153</v>
       </c>
       <c r="F74" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4738,22 +4759,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4782,13 +4803,13 @@
         <v>46167</v>
       </c>
       <c r="E75" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F75" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G75" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4797,22 +4818,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4824,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="S75" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
@@ -4841,13 +4862,13 @@
         <v>46167</v>
       </c>
       <c r="E76" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4856,22 +4877,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4883,7 +4904,7 @@
         <v>29</v>
       </c>
       <c r="S76" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -4900,13 +4921,13 @@
         <v>46167</v>
       </c>
       <c r="E77" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F77" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G77" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4915,22 +4936,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4942,7 +4963,7 @@
         <v>29</v>
       </c>
       <c r="S77" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -4962,10 +4983,10 @@
         <v>46119</v>
       </c>
       <c r="F78" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -4974,22 +4995,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -4998,10 +5019,10 @@
         <v>37</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S78" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
@@ -5018,13 +5039,13 @@
         <v>46167</v>
       </c>
       <c r="E79" s="7">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="F79" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5033,22 +5054,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5057,7 +5078,7 @@
         <v>37</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S79" s="9">
         <v>680</v>
@@ -5077,13 +5098,13 @@
         <v>46167</v>
       </c>
       <c r="E80" s="7">
-        <v>46099</v>
+        <v>46119</v>
       </c>
       <c r="F80" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G80" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5092,22 +5113,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5116,10 +5137,10 @@
         <v>37</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S80" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
@@ -5136,13 +5157,13 @@
         <v>46167</v>
       </c>
       <c r="E81" s="7">
-        <v>46160</v>
+        <v>46119</v>
       </c>
       <c r="F81" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G81" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5151,34 +5172,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="S81" s="9">
-        <v>1200</v>
+        <v>680</v>
       </c>
     </row>
     <row r="82" ht="23" customHeight="1">
@@ -5195,13 +5216,13 @@
         <v>46167</v>
       </c>
       <c r="E82" s="7">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="F82" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5216,28 +5237,28 @@
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="S82" s="9">
-        <v>1200</v>
+        <v>680</v>
       </c>
     </row>
     <row r="83" ht="23" customHeight="1">
@@ -5248,43 +5269,43 @@
         <v>46167</v>
       </c>
       <c r="C83" s="7">
-        <v>46113</v>
+        <v>46167</v>
       </c>
       <c r="D83" s="7">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="E83" s="7">
-        <v>46149</v>
+        <v>46164</v>
       </c>
       <c r="F83" s="8">
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="G83" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5293,69 +5314,305 @@
         <v>37</v>
       </c>
       <c r="R83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S83" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F84" s="8">
+        <v>3</v>
+      </c>
+      <c r="G84" s="8">
+        <v>3</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S84" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F85" s="8">
+        <v>3</v>
+      </c>
+      <c r="G85" s="8">
+        <v>3</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="S85" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="86" ht="23" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F86" s="8">
+        <v>3</v>
+      </c>
+      <c r="G86" s="8">
+        <v>3</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="S86" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F87" s="8">
+        <v>-14</v>
+      </c>
+      <c r="G87" s="8">
+        <v>3</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R87" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="S83" s="9">
+      <c r="S87" s="9">
         <v>4400</v>
       </c>
     </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R84" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S84" s="13">
-        <f>SUM(S6:S83)</f>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S88" s="13">
+        <f>SUM(S6:S87)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 25 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em terça-feira, 26 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -235,153 +235,153 @@
     <t>FA-11557</t>
   </si>
   <si>
-    <t>FA-11471</t>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
   </si>
   <si>
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11675</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11674</t>
+  </si>
+  <si>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>FA-11667</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
     <t>FA-11473</t>
   </si>
   <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11675</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>FA-11674</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>FA-11667</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
     <t>FA-11480</t>
   </si>
   <si>
@@ -397,15 +397,12 @@
     <t>FA-11668</t>
   </si>
   <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
     <t>FA-11494</t>
   </si>
   <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
     <t>FA-11683</t>
   </si>
   <si>
@@ -418,15 +415,15 @@
     <t>FA-11488</t>
   </si>
   <si>
+    <t>FA-11621</t>
+  </si>
+  <si>
     <t>FA-11504</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
     <t>FA-11656</t>
   </si>
   <si>
@@ -439,24 +436,24 @@
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11691</t>
+  </si>
+  <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
     <t>FA-11412</t>
   </si>
   <si>
     <t>FA-11491</t>
   </si>
   <si>
-    <t>FA-11691</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11676</t>
-  </si>
-  <si>
     <t>FA-11329</t>
   </si>
   <si>
@@ -478,6 +475,15 @@
     <t>ELIONILSON CORDEIRO BARBOSA</t>
   </si>
   <si>
+    <t>FA-11644</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
   </si>
   <si>
@@ -494,15 +500,6 @@
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11644</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
     <t>FA-11613</t>
@@ -771,10 +768,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="G6" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -830,10 +827,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G7" s="8">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -889,10 +886,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G8" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -948,10 +945,10 @@
         <v>46127</v>
       </c>
       <c r="F9" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G9" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>35</v>
@@ -1007,10 +1004,10 @@
         <v>46097</v>
       </c>
       <c r="F10" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G10" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>35</v>
@@ -1066,10 +1063,10 @@
         <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G11" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1125,10 +1122,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="G12" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1184,10 +1181,10 @@
         <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G13" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1243,10 +1240,10 @@
         <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>35</v>
@@ -1302,10 +1299,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G15" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>35</v>
@@ -1361,10 +1358,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G16" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>35</v>
@@ -1420,10 +1417,10 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G17" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>35</v>
@@ -1479,10 +1476,10 @@
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G18" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>35</v>
@@ -1538,10 +1535,10 @@
         <v>46141</v>
       </c>
       <c r="F19" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G19" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>35</v>
@@ -1597,10 +1594,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G20" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>24</v>
@@ -1656,10 +1653,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G21" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>35</v>
@@ -1715,10 +1712,10 @@
         <v>46148</v>
       </c>
       <c r="F22" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G22" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>35</v>
@@ -1774,10 +1771,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G23" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>24</v>
@@ -1833,10 +1830,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G24" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>35</v>
@@ -1892,10 +1889,10 @@
         <v>46153</v>
       </c>
       <c r="F25" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G25" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>35</v>
@@ -1951,10 +1948,10 @@
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G26" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>64</v>
@@ -2010,10 +2007,10 @@
         <v>46097</v>
       </c>
       <c r="F27" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G27" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>35</v>
@@ -2069,10 +2066,10 @@
         <v>46141</v>
       </c>
       <c r="F28" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G28" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>35</v>
@@ -2128,10 +2125,10 @@
         <v>46119</v>
       </c>
       <c r="F29" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G29" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>35</v>
@@ -2146,10 +2143,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2164,10 +2161,10 @@
         <v>37</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S29" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2175,19 +2172,19 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C30" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D30" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E30" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="G30" s="8">
         <v>-14</v>
@@ -2199,16 +2196,16 @@
         <v>35</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="M30" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2220,13 +2217,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>650</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2234,40 +2231,40 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C31" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D31" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="G31" s="8">
         <v>-14</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="M31" s="6" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2279,13 +2276,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2293,25 +2290,25 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C32" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D32" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-21</v>
+        <v>-36</v>
       </c>
       <c r="G32" s="8">
         <v>-13</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>35</v>
@@ -2323,7 +2320,7 @@
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2344,7 +2341,7 @@
         <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>280</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2352,40 +2349,40 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C33" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D33" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-35</v>
+        <v>-29</v>
       </c>
       <c r="G33" s="8">
         <v>-13</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="M33" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2403,7 +2400,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>317.54</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2414,22 +2411,22 @@
         <v>46155</v>
       </c>
       <c r="C34" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="D34" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="G34" s="8">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>35</v>
@@ -2441,7 +2438,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2462,7 +2459,7 @@
         <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>140</v>
+        <v>530</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2470,19 +2467,19 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C35" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D35" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-28</v>
+        <v>-22</v>
       </c>
       <c r="G35" s="8">
         <v>-12</v>
@@ -2500,10 +2497,10 @@
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2521,7 +2518,7 @@
         <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>250</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2529,22 +2526,22 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C36" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D36" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G36" s="8">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>35</v>
@@ -2553,13 +2550,13 @@
         <v>35</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2580,7 +2577,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>530</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2588,22 +2585,22 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="C37" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D37" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46097</v>
       </c>
       <c r="F37" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="G37" s="8">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>35</v>
@@ -2612,13 +2609,13 @@
         <v>35</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2633,13 +2630,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S37" s="9">
-        <v>130</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2655,14 +2652,14 @@
       <c r="D38" s="7">
         <v>46160</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+      <c r="E38" s="7">
+        <v>46127</v>
       </c>
       <c r="F38" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G38" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>35</v>
@@ -2671,16 +2668,16 @@
         <v>35</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2692,13 +2689,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>97.5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2709,19 +2706,19 @@
         <v>46160</v>
       </c>
       <c r="C39" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D39" s="7">
         <v>46160</v>
       </c>
       <c r="E39" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F39" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G39" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>35</v>
@@ -2730,13 +2727,13 @@
         <v>35</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2751,13 +2748,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2768,37 +2765,37 @@
         <v>46160</v>
       </c>
       <c r="C40" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D40" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46127</v>
+        <v>46132</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-7</v>
+        <v>-36</v>
       </c>
       <c r="G40" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2810,13 +2807,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S40" s="9">
-        <v>172</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2827,19 +2824,19 @@
         <v>46160</v>
       </c>
       <c r="C41" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D41" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46141</v>
+        <v>46146</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="G41" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>35</v>
@@ -2848,16 +2845,16 @@
         <v>35</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2869,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>310</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2886,37 +2883,37 @@
         <v>46160</v>
       </c>
       <c r="C42" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D42" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46119</v>
       </c>
       <c r="F42" s="8">
-        <v>-35</v>
+        <v>-8</v>
       </c>
       <c r="G42" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>27</v>
@@ -2928,13 +2925,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2945,19 +2942,19 @@
         <v>46160</v>
       </c>
       <c r="C43" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D43" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46119</v>
       </c>
       <c r="F43" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="G43" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>35</v>
@@ -2972,10 +2969,10 @@
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2987,13 +2984,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S43" s="9">
-        <v>450</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -3010,13 +3007,13 @@
         <v>46160</v>
       </c>
       <c r="E44" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F44" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G44" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>35</v>
@@ -3025,16 +3022,16 @@
         <v>35</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -3052,7 +3049,7 @@
         <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3069,13 +3066,13 @@
         <v>46160</v>
       </c>
       <c r="E45" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F45" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G45" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>35</v>
@@ -3084,16 +3081,16 @@
         <v>35</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -3111,7 +3108,7 @@
         <v>29</v>
       </c>
       <c r="S45" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3128,13 +3125,13 @@
         <v>46160</v>
       </c>
       <c r="E46" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F46" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G46" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>35</v>
@@ -3143,16 +3140,16 @@
         <v>35</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3167,10 +3164,10 @@
         <v>37</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3187,13 +3184,13 @@
         <v>46160</v>
       </c>
       <c r="E47" s="7">
-        <v>46112</v>
+        <v>46153</v>
       </c>
       <c r="F47" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G47" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>35</v>
@@ -3208,7 +3205,7 @@
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3229,7 +3226,7 @@
         <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3246,13 +3243,13 @@
         <v>46160</v>
       </c>
       <c r="E48" s="7">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="F48" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G48" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>35</v>
@@ -3267,7 +3264,7 @@
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3285,10 +3282,10 @@
         <v>37</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S48" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3308,10 +3305,10 @@
         <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G49" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>35</v>
@@ -3320,16 +3317,16 @@
         <v>35</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3347,7 +3344,7 @@
         <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3364,13 +3361,13 @@
         <v>46160</v>
       </c>
       <c r="E50" s="7">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="F50" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G50" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>35</v>
@@ -3379,13 +3376,13 @@
         <v>35</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3403,10 +3400,10 @@
         <v>37</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S50" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3426,10 +3423,10 @@
         <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G51" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>35</v>
@@ -3438,7 +3435,7 @@
         <v>35</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
@@ -3482,13 +3479,13 @@
         <v>46160</v>
       </c>
       <c r="E52" s="7">
-        <v>46164</v>
+        <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G52" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>35</v>
@@ -3497,13 +3494,13 @@
         <v>35</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3515,16 +3512,16 @@
         <v>27</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3532,19 +3529,19 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C53" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D53" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E53" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-7</v>
+        <v>-29</v>
       </c>
       <c r="G53" s="8">
         <v>-7</v>
@@ -3556,13 +3553,13 @@
         <v>35</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3574,16 +3571,16 @@
         <v>27</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3591,7 +3588,7 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C54" s="7">
         <v>46160</v>
@@ -3599,11 +3596,11 @@
       <c r="D54" s="7">
         <v>46160</v>
       </c>
-      <c r="E54" s="7">
-        <v>46141</v>
+      <c r="E54" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G54" s="8">
         <v>-7</v>
@@ -3615,13 +3612,13 @@
         <v>35</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3636,13 +3633,13 @@
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S54" s="9">
-        <v>680</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3650,19 +3647,19 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C55" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D55" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G55" s="8">
         <v>-7</v>
@@ -3674,16 +3671,16 @@
         <v>35</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N55" s="6" t="s">
         <v>27</v>
@@ -3692,16 +3689,16 @@
         <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S55" s="9">
-        <v>700</v>
+        <v>277.36</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3712,19 +3709,19 @@
         <v>46161</v>
       </c>
       <c r="C56" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="D56" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-28</v>
+        <v>-15</v>
       </c>
       <c r="G56" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>35</v>
@@ -3733,13 +3730,13 @@
         <v>35</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3751,16 +3748,16 @@
         <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S56" s="9">
-        <v>50</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3771,20 +3768,20 @@
         <v>46161</v>
       </c>
       <c r="C57" s="7">
-        <v>46160</v>
+        <v>46113</v>
       </c>
       <c r="D57" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46149</v>
       </c>
       <c r="F57" s="8">
+        <v>-18</v>
+      </c>
+      <c r="G57" s="8">
         <v>-7</v>
       </c>
-      <c r="G57" s="8">
-        <v>-6</v>
-      </c>
       <c r="H57" s="6" t="s">
         <v>35</v>
       </c>
@@ -3792,16 +3789,16 @@
         <v>35</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3813,13 +3810,13 @@
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>130</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3827,40 +3824,40 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C58" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="D58" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>-14</v>
+        <v>-43</v>
       </c>
       <c r="G58" s="8">
         <v>-6</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3878,7 +3875,7 @@
         <v>32</v>
       </c>
       <c r="S58" s="9">
-        <v>277.36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3886,19 +3883,19 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C59" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D59" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F59" s="8">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="G59" s="8">
         <v>-6</v>
@@ -3910,16 +3907,16 @@
         <v>35</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3934,10 +3931,10 @@
         <v>23</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3945,19 +3942,19 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C60" s="7">
-        <v>46113</v>
+        <v>46160</v>
       </c>
       <c r="D60" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46149</v>
+        <v>46160</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F60" s="8">
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="G60" s="8">
         <v>-6</v>
@@ -3969,16 +3966,16 @@
         <v>35</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>27</v>
@@ -3990,13 +3987,13 @@
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>2100</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -4004,25 +4001,25 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C61" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="D61" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>-42</v>
+        <v>-8</v>
       </c>
       <c r="G61" s="8">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>35</v>
@@ -4034,7 +4031,7 @@
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
@@ -4052,10 +4049,10 @@
         <v>23</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>50</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4063,22 +4060,22 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C62" s="7">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="D62" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46153</v>
       </c>
       <c r="F62" s="8">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="G62" s="8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>35</v>
@@ -4093,10 +4090,10 @@
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
         <v>27</v>
@@ -4105,16 +4102,16 @@
         <v>27</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S62" s="9">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4122,22 +4119,22 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C63" s="7">
-        <v>46160</v>
+        <v>46143</v>
       </c>
       <c r="D63" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46167</v>
       </c>
       <c r="F63" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G63" s="8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>35</v>
@@ -4146,13 +4143,13 @@
         <v>35</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
@@ -4167,13 +4164,13 @@
         <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S63" s="9">
-        <v>380</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4181,22 +4178,22 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C64" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D64" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F64" s="8">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G64" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>35</v>
@@ -4205,13 +4202,13 @@
         <v>35</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
@@ -4232,7 +4229,7 @@
         <v>29</v>
       </c>
       <c r="S64" s="9">
-        <v>290</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4243,34 +4240,34 @@
         <v>46167</v>
       </c>
       <c r="C65" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D65" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46097</v>
       </c>
       <c r="F65" s="8">
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
@@ -4279,19 +4276,19 @@
         <v>27</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S65" s="9">
-        <v>130</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4302,55 +4299,55 @@
         <v>46167</v>
       </c>
       <c r="C66" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D66" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E66" s="7">
-        <v>46097</v>
+        <v>46153</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S66" s="9">
-        <v>146.55</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4370,16 +4367,16 @@
         <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>116</v>
@@ -4388,16 +4385,16 @@
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4429,16 +4426,16 @@
         <v>46141</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G68" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>117</v>
@@ -4453,10 +4450,10 @@
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4488,16 +4485,16 @@
         <v>46119</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J69" s="6" t="s">
         <v>118</v>
@@ -4506,16 +4503,16 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4547,16 +4544,16 @@
         <v>46141</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G70" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>119</v>
@@ -4571,10 +4568,10 @@
         <v>87</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4606,16 +4603,16 @@
         <v>46163</v>
       </c>
       <c r="F71" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G71" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>120</v>
@@ -4630,10 +4627,10 @@
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4662,19 +4659,19 @@
         <v>46167</v>
       </c>
       <c r="E72" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>121</v>
@@ -4683,19 +4680,19 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>37</v>
@@ -4721,40 +4718,40 @@
         <v>46167</v>
       </c>
       <c r="E73" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G73" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q73" s="6" t="s">
         <v>37</v>
@@ -4783,34 +4780,34 @@
         <v>46164</v>
       </c>
       <c r="F74" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G74" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J74" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K74" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4842,34 +4839,34 @@
         <v>46092</v>
       </c>
       <c r="F75" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G75" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4901,34 +4898,34 @@
         <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G76" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4957,37 +4954,37 @@
         <v>46167</v>
       </c>
       <c r="E77" s="7">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="F77" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5016,37 +5013,37 @@
         <v>46167</v>
       </c>
       <c r="E78" s="7">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="F78" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5078,34 +5075,34 @@
         <v>46160</v>
       </c>
       <c r="F79" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G79" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J79" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="K79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5137,34 +5134,34 @@
         <v>46119</v>
       </c>
       <c r="F80" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G80" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J80" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="K80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5193,37 +5190,37 @@
         <v>46167</v>
       </c>
       <c r="E81" s="7">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="F81" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G81" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5232,7 +5229,7 @@
         <v>37</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S81" s="9">
         <v>680</v>
@@ -5255,34 +5252,34 @@
         <v>46119</v>
       </c>
       <c r="F82" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5291,7 +5288,7 @@
         <v>37</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S82" s="9">
         <v>680</v>
@@ -5314,19 +5311,19 @@
         <v>46167</v>
       </c>
       <c r="F83" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G83" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
@@ -5338,10 +5335,10 @@
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5370,37 +5367,37 @@
         <v>46167</v>
       </c>
       <c r="E84" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F84" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G84" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5429,37 +5426,37 @@
         <v>46167</v>
       </c>
       <c r="E85" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F85" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G85" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5488,37 +5485,37 @@
         <v>46167</v>
       </c>
       <c r="E86" s="7">
-        <v>46164</v>
+        <v>46119</v>
       </c>
       <c r="F86" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G86" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5550,34 +5547,34 @@
         <v>46099</v>
       </c>
       <c r="F87" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G87" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J87" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="K87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5594,7 +5591,7 @@
     </row>
     <row r="88" ht="23" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B88" s="7">
         <v>46167</v>
@@ -5609,34 +5606,34 @@
         <v>46148</v>
       </c>
       <c r="F88" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G88" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J88" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5653,7 +5650,7 @@
     </row>
     <row r="89" ht="23" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B89" s="7">
         <v>46167</v>
@@ -5668,34 +5665,34 @@
         <v>46129</v>
       </c>
       <c r="F89" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G89" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J89" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5712,52 +5709,52 @@
     </row>
     <row r="90" ht="23" customHeight="1">
       <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F90" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G90" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F90" s="8">
-        <v>0</v>
-      </c>
-      <c r="G90" s="8">
-        <v>0</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" s="6" t="s">
+      <c r="M90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>37</v>
@@ -5771,7 +5768,7 @@
     </row>
     <row r="91" ht="23" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B91" s="7">
         <v>46167</v>
@@ -5786,16 +5783,16 @@
         <v>46148</v>
       </c>
       <c r="F91" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G91" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J91" s="6" t="s">
         <v>151</v>
@@ -5804,16 +5801,16 @@
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5830,7 +5827,7 @@
     </row>
     <row r="92" ht="23" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="B92" s="7">
         <v>46167</v>
@@ -5842,40 +5839,40 @@
         <v>46167</v>
       </c>
       <c r="E92" s="7">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="F92" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G92" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>37</v>
@@ -5904,37 +5901,37 @@
         <v>46160</v>
       </c>
       <c r="F93" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G93" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J93" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>156</v>
-      </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>37</v>
@@ -5963,34 +5960,34 @@
         <v>46149</v>
       </c>
       <c r="F94" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G94" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J94" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
+      <c r="M94" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="M94" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="N94" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$61</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -175,12 +175,6 @@
     <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
   </si>
   <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
     <t>FA-11703</t>
   </si>
   <si>
@@ -199,12 +193,6 @@
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
   </si>
   <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
     <t>FA-11557</t>
   </si>
   <si>
@@ -217,49 +205,88 @@
     <t>FA-11478</t>
   </si>
   <si>
-    <t>FA-11757</t>
-  </si>
-  <si>
     <t>FA-11614</t>
   </si>
   <si>
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11453</t>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11707</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
   </si>
   <si>
     <t>DERICK PEDRO BEZERRA DA ROCHA</t>
   </si>
   <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>FA-11667</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
   </si>
   <si>
     <t>FA-11481</t>
@@ -268,60 +295,6 @@
     <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
   </si>
   <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11707</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11758</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>FA-11667</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
     <t>FA-11280</t>
   </si>
   <si>
@@ -340,30 +313,24 @@
     <t>FA-11480</t>
   </si>
   <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
     <t>FA-11563</t>
   </si>
   <si>
-    <t>FA-11487</t>
+    <t>FA-11715</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
   </si>
   <si>
     <t>FA-11668</t>
   </si>
   <si>
-    <t>FA-11715</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>FA-11617</t>
   </si>
   <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
     <t>FA-11709</t>
   </si>
   <si>
@@ -373,7 +340,16 @@
     <t>FA-11491</t>
   </si>
   <si>
-    <t>FA-11759</t>
+    <t>FA-11691</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
   </si>
   <si>
     <t>FA-11676</t>
@@ -386,18 +362,6 @@
   </si>
   <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11691</t>
   </si>
   <si>
     <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
@@ -549,7 +513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -1370,8 +1334,8 @@
       <c r="D18" s="7">
         <v>46146</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>23</v>
+      <c r="E18" s="7">
+        <v>46168</v>
       </c>
       <c r="F18" s="8">
         <v>-23</v>
@@ -1392,7 +1356,7 @@
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
@@ -1407,13 +1371,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S18" s="9">
-        <v>205.82</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1421,22 +1385,22 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C19" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D19" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="E19" s="7">
-        <v>46168</v>
+        <v>46148</v>
       </c>
       <c r="F19" s="8">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="G19" s="8">
-        <v>-23</v>
+        <v>-20</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>33</v>
@@ -1445,13 +1409,13 @@
         <v>33</v>
       </c>
       <c r="J19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>23</v>
@@ -1469,10 +1433,10 @@
         <v>35</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="S19" s="9">
-        <v>650</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1480,37 +1444,37 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C20" s="7">
-        <v>46142</v>
+        <v>46125</v>
       </c>
       <c r="D20" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E20" s="7">
-        <v>46148</v>
+        <v>46125</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-27</v>
+        <v>-44</v>
       </c>
       <c r="G20" s="8">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1525,13 +1489,13 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>685.71</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1539,37 +1503,37 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C21" s="7">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="D21" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-44</v>
+        <v>-16</v>
       </c>
       <c r="G21" s="8">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1584,13 +1548,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S21" s="9">
-        <v>53.82</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1598,22 +1562,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C22" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D22" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E22" s="7">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="F22" s="8">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="G22" s="8">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>33</v>
@@ -1622,13 +1586,13 @@
         <v>33</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
@@ -1649,7 +1613,7 @@
         <v>29</v>
       </c>
       <c r="S22" s="9">
-        <v>278.57</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1660,13 +1624,13 @@
         <v>46153</v>
       </c>
       <c r="C23" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D23" s="7">
         <v>46153</v>
       </c>
       <c r="E23" s="7">
-        <v>46097</v>
+        <v>46168</v>
       </c>
       <c r="F23" s="8">
         <v>-16</v>
@@ -1681,13 +1645,13 @@
         <v>33</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1702,13 +1666,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>32</v>
       </c>
       <c r="S23" s="9">
-        <v>146.55</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1725,7 +1689,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F24" s="8">
         <v>-16</v>
@@ -1740,13 +1704,13 @@
         <v>33</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1764,10 +1728,10 @@
         <v>35</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S24" s="9">
-        <v>310</v>
+        <v>680</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1775,22 +1739,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C25" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D25" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46168</v>
+        <v>46146</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="G25" s="8">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>33</v>
@@ -1799,13 +1763,13 @@
         <v>33</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -1820,13 +1784,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>650</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1834,7 +1798,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C26" s="7">
         <v>46153</v>
@@ -1842,14 +1806,14 @@
       <c r="D26" s="7">
         <v>46153</v>
       </c>
-      <c r="E26" s="7">
-        <v>46119</v>
+      <c r="E26" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F26" s="8">
         <v>-16</v>
       </c>
       <c r="G26" s="8">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>33</v>
@@ -1858,13 +1822,13 @@
         <v>33</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1879,13 +1843,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S26" s="9">
-        <v>680</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1893,22 +1857,22 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C27" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D27" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46169</v>
+        <v>46160</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>33</v>
@@ -1917,13 +1881,13 @@
         <v>33</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1938,13 +1902,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>680</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1952,22 +1916,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C28" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D28" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46097</v>
       </c>
       <c r="F28" s="8">
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>33</v>
@@ -1976,13 +1940,13 @@
         <v>33</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -1997,13 +1961,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S28" s="9">
-        <v>280</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2011,40 +1975,40 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C29" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D29" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46127</v>
       </c>
       <c r="F29" s="8">
-        <v>-37</v>
+        <v>-9</v>
       </c>
       <c r="G29" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2056,13 +2020,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>317.54</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2070,22 +2034,22 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C30" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D30" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46141</v>
       </c>
       <c r="F30" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>33</v>
@@ -2094,13 +2058,13 @@
         <v>33</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2115,13 +2079,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>530</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2132,34 +2096,34 @@
         <v>46160</v>
       </c>
       <c r="C31" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D31" s="7">
-        <v>46160</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-9</v>
+        <v>-37</v>
       </c>
       <c r="G31" s="8">
         <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2177,10 +2141,10 @@
         <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S31" s="9">
-        <v>97.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2191,13 +2155,13 @@
         <v>46160</v>
       </c>
       <c r="C32" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D32" s="7">
         <v>46160</v>
       </c>
       <c r="E32" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F32" s="8">
         <v>-9</v>
@@ -2212,16 +2176,16 @@
         <v>33</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2233,13 +2197,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2256,7 +2220,7 @@
         <v>46160</v>
       </c>
       <c r="E33" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F33" s="8">
         <v>-9</v>
@@ -2271,16 +2235,16 @@
         <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="M33" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2298,7 +2262,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>172</v>
+        <v>620</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2315,7 +2279,7 @@
         <v>46160</v>
       </c>
       <c r="E34" s="7">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="F34" s="8">
         <v>-9</v>
@@ -2330,7 +2294,7 @@
         <v>33</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
@@ -2357,7 +2321,7 @@
         <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>310</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2368,28 +2332,28 @@
         <v>46160</v>
       </c>
       <c r="C35" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46168</v>
       </c>
       <c r="F35" s="8">
-        <v>-37</v>
+        <v>-9</v>
       </c>
       <c r="G35" s="8">
         <v>-9</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
@@ -2410,13 +2374,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>32</v>
       </c>
       <c r="S35" s="9">
-        <v>350</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2427,16 +2391,16 @@
         <v>46160</v>
       </c>
       <c r="C36" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D36" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46119</v>
       </c>
       <c r="F36" s="8">
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G36" s="8">
         <v>-9</v>
@@ -2448,16 +2412,16 @@
         <v>33</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2469,13 +2433,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S36" s="9">
-        <v>450</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2507,16 +2471,16 @@
         <v>33</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="M37" s="6" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2525,7 +2489,7 @@
         <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>35</v>
@@ -2534,7 +2498,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2542,22 +2506,22 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C38" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D38" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-9</v>
+        <v>-30</v>
       </c>
       <c r="G38" s="8">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>33</v>
@@ -2566,16 +2530,16 @@
         <v>33</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2584,16 +2548,16 @@
         <v>27</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>620</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2601,22 +2565,22 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C39" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D39" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G39" s="8">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>33</v>
@@ -2625,16 +2589,16 @@
         <v>33</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2646,13 +2610,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>620</v>
+        <v>179.12</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2660,37 +2624,37 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C40" s="7">
-        <v>46160</v>
+        <v>46125</v>
       </c>
       <c r="D40" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46150</v>
+        <v>46125</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-9</v>
+        <v>-44</v>
       </c>
       <c r="G40" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2705,13 +2669,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S40" s="9">
-        <v>630</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2719,22 +2683,22 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C41" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D41" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46153</v>
+        <v>46146</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G41" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>33</v>
@@ -2743,16 +2707,16 @@
         <v>33</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2764,13 +2728,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>650</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2778,7 +2742,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C42" s="7">
         <v>46160</v>
@@ -2786,14 +2750,14 @@
       <c r="D42" s="7">
         <v>46160</v>
       </c>
-      <c r="E42" s="7">
-        <v>46168</v>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
         <v>-9</v>
       </c>
       <c r="G42" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>33</v>
@@ -2802,13 +2766,13 @@
         <v>33</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2823,13 +2787,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>650</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2837,22 +2801,22 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="C43" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D43" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G43" s="8">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>33</v>
@@ -2861,13 +2825,13 @@
         <v>33</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2882,13 +2846,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>680</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2896,7 +2860,7 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C44" s="7">
         <v>46160</v>
@@ -2904,14 +2868,14 @@
       <c r="D44" s="7">
         <v>46160</v>
       </c>
-      <c r="E44" s="7">
-        <v>46169</v>
+      <c r="E44" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F44" s="8">
         <v>-9</v>
       </c>
       <c r="G44" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>33</v>
@@ -2920,13 +2884,13 @@
         <v>33</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -2941,13 +2905,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>680</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -2955,22 +2919,22 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C45" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D45" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E45" s="7">
-        <v>46119</v>
+        <v>46097</v>
       </c>
       <c r="F45" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G45" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>33</v>
@@ -2979,13 +2943,13 @@
         <v>33</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3000,13 +2964,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S45" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3014,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C46" s="7">
         <v>46160</v>
@@ -3022,14 +2986,14 @@
       <c r="D46" s="7">
         <v>46160</v>
       </c>
-      <c r="E46" s="7">
-        <v>46119</v>
+      <c r="E46" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F46" s="8">
         <v>-9</v>
       </c>
       <c r="G46" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>33</v>
@@ -3038,13 +3002,13 @@
         <v>33</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3056,16 +3020,16 @@
         <v>27</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>700</v>
+        <v>210.87</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3073,22 +3037,22 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="C47" s="7">
-        <v>46139</v>
+        <v>46167</v>
       </c>
       <c r="D47" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46141</v>
       </c>
       <c r="F47" s="8">
-        <v>-30</v>
+        <v>-2</v>
       </c>
       <c r="G47" s="8">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>33</v>
@@ -3097,13 +3061,13 @@
         <v>33</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3115,16 +3079,16 @@
         <v>27</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>50</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3132,22 +3096,22 @@
         <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="C48" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D48" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G48" s="8">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>33</v>
@@ -3156,16 +3120,16 @@
         <v>33</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3183,7 +3147,7 @@
         <v>32</v>
       </c>
       <c r="S48" s="9">
-        <v>277.36</v>
+        <v>337.36</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3191,37 +3155,37 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C49" s="7">
-        <v>46125</v>
+        <v>46167</v>
       </c>
       <c r="D49" s="7">
-        <v>46125</v>
+        <v>46167</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>-44</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3239,10 +3203,10 @@
         <v>23</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>50</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3250,22 +3214,22 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C50" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D50" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="G50" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>33</v>
@@ -3274,16 +3238,16 @@
         <v>33</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
@@ -3301,7 +3265,7 @@
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3309,7 +3273,7 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C51" s="7">
         <v>46160</v>
@@ -3324,7 +3288,7 @@
         <v>-9</v>
       </c>
       <c r="G51" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>33</v>
@@ -3333,13 +3297,13 @@
         <v>33</v>
       </c>
       <c r="J51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3360,7 +3324,7 @@
         <v>29</v>
       </c>
       <c r="S51" s="9">
-        <v>380</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3368,22 +3332,22 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C52" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D52" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>-23</v>
+        <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>33</v>
@@ -3398,10 +3362,10 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3413,13 +3377,13 @@
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>210</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3430,16 +3394,16 @@
         <v>46167</v>
       </c>
       <c r="C53" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D53" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46119</v>
       </c>
       <c r="F53" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G53" s="8">
         <v>-2</v>
@@ -3457,10 +3421,10 @@
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>27</v>
@@ -3472,13 +3436,13 @@
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S53" s="9">
-        <v>140</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3489,13 +3453,13 @@
         <v>46167</v>
       </c>
       <c r="C54" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D54" s="7">
         <v>46167</v>
       </c>
       <c r="E54" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
         <v>-2</v>
@@ -3510,16 +3474,16 @@
         <v>33</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>27</v>
@@ -3531,13 +3495,13 @@
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S54" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3554,7 +3518,7 @@
         <v>46167</v>
       </c>
       <c r="E55" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F55" s="8">
         <v>-2</v>
@@ -3575,7 +3539,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3596,7 +3560,7 @@
         <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>310</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3612,8 +3576,8 @@
       <c r="D56" s="7">
         <v>46167</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>23</v>
+      <c r="E56" s="7">
+        <v>46163</v>
       </c>
       <c r="F56" s="8">
         <v>-2</v>
@@ -3628,13 +3592,13 @@
         <v>33</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3649,13 +3613,13 @@
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>350</v>
+        <v>630</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3666,16 +3630,16 @@
         <v>46167</v>
       </c>
       <c r="C57" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D57" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46150</v>
       </c>
       <c r="F57" s="8">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="G57" s="8">
         <v>-2</v>
@@ -3693,10 +3657,10 @@
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3708,13 +3672,13 @@
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3725,16 +3689,16 @@
         <v>46167</v>
       </c>
       <c r="C58" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D58" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46168</v>
       </c>
       <c r="F58" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G58" s="8">
         <v>-2</v>
@@ -3752,7 +3716,7 @@
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
@@ -3767,13 +3731,13 @@
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S58" s="9">
-        <v>572.72</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3790,7 +3754,7 @@
         <v>46167</v>
       </c>
       <c r="E59" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F59" s="8">
         <v>-2</v>
@@ -3805,16 +3769,16 @@
         <v>33</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3832,7 +3796,7 @@
         <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3849,7 +3813,7 @@
         <v>46167</v>
       </c>
       <c r="E60" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F60" s="8">
         <v>-2</v>
@@ -3864,16 +3828,16 @@
         <v>33</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>27</v>
@@ -3888,10 +3852,10 @@
         <v>35</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S60" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3908,7 +3872,7 @@
         <v>46167</v>
       </c>
       <c r="E61" s="7">
-        <v>46119</v>
+        <v>46167</v>
       </c>
       <c r="F61" s="8">
         <v>-2</v>
@@ -3923,16 +3887,16 @@
         <v>33</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>27</v>
@@ -3947,10 +3911,10 @@
         <v>35</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -3967,7 +3931,7 @@
         <v>46167</v>
       </c>
       <c r="E62" s="7">
-        <v>46163</v>
+        <v>46119</v>
       </c>
       <c r="F62" s="8">
         <v>-2</v>
@@ -3982,13 +3946,13 @@
         <v>33</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
@@ -4009,7 +3973,7 @@
         <v>29</v>
       </c>
       <c r="S62" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4026,7 +3990,7 @@
         <v>46167</v>
       </c>
       <c r="E63" s="7">
-        <v>46169</v>
+        <v>46141</v>
       </c>
       <c r="F63" s="8">
         <v>-2</v>
@@ -4041,13 +4005,13 @@
         <v>33</v>
       </c>
       <c r="J63" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
@@ -4065,10 +4029,10 @@
         <v>35</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S63" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4085,7 +4049,7 @@
         <v>46167</v>
       </c>
       <c r="E64" s="7">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="F64" s="8">
         <v>-2</v>
@@ -4100,13 +4064,13 @@
         <v>33</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
@@ -4124,10 +4088,10 @@
         <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S64" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4144,7 +4108,7 @@
         <v>46167</v>
       </c>
       <c r="E65" s="7">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="F65" s="8">
         <v>-2</v>
@@ -4165,7 +4129,7 @@
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
@@ -4186,12 +4150,12 @@
         <v>29</v>
       </c>
       <c r="S65" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B66" s="7">
         <v>46167</v>
@@ -4203,7 +4167,7 @@
         <v>46167</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="F66" s="8">
         <v>-2</v>
@@ -4218,16 +4182,16 @@
         <v>33</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
         <v>27</v>
@@ -4242,659 +4206,69 @@
         <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S66" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
-      <c r="A67" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B67" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C67" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D67" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F67" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G67" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J67" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N67" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O67" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q67" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R67" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S67" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="68" ht="23" customHeight="1">
-      <c r="A68" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C68" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D68" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E68" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F68" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G68" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J68" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q68" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R68" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S68" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="69" ht="23" customHeight="1">
-      <c r="A69" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B69" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C69" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D69" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E69" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F69" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G69" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J69" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M69" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N69" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O69" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P69" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q69" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R69" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S69" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="70" ht="23" customHeight="1">
-      <c r="A70" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C70" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D70" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E70" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F70" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G70" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J70" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M70" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q70" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R70" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S70" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="71" ht="23" customHeight="1">
-      <c r="A71" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B71" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C71" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D71" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E71" s="7">
-        <v>46164</v>
-      </c>
-      <c r="F71" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G71" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L71" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O71" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q71" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R71" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S71" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="72" ht="23" customHeight="1">
-      <c r="A72" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B72" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C72" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D72" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E72" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F72" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G72" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J72" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N72" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q72" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R72" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S72" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="73" ht="23" customHeight="1">
-      <c r="A73" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B73" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C73" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D73" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E73" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F73" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G73" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M73" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O73" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P73" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q73" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S73" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="74" ht="23" customHeight="1">
-      <c r="A74" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C74" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D74" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E74" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F74" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G74" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q74" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R74" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S74" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="75" ht="23" customHeight="1">
-      <c r="A75" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B75" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C75" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D75" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E75" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F75" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G75" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L75" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N75" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O75" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q75" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R75" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S75" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="76" ht="23" customHeight="1">
-      <c r="A76" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B76" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C76" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D76" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E76" s="7">
-        <v>46129</v>
-      </c>
-      <c r="F76" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G76" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N76" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q76" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R76" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S76" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="77" ht="23" customHeight="1">
-      <c r="A77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R77" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S77" s="13">
-        <f>SUM(S6:S76)</f>
+      <c r="A67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S67" s="13">
+        <f>SUM(S6:S66)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$46</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -145,223 +145,169 @@
     <t>NOTA DE DÉBITO</t>
   </si>
   <si>
-    <t>FA-11701</t>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11667</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11715</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
   </si>
   <si>
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>ND-11574</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11703</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11705</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11707</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>FA-11667</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11715</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>FA-11709</t>
-  </si>
-  <si>
     <t>FA-11412</t>
   </si>
   <si>
     <t>FA-11491</t>
   </si>
   <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11710</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11691</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11676</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11710</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
     <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
@@ -513,7 +459,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -528,7 +474,7 @@
     <col min="10" max="10" width="25.261001586914062" customWidth="1" style="1"/>
     <col min="11" max="11" width="15.191652297973633" customWidth="1" style="1"/>
     <col min="12" max="12" width="43.70395278930664" customWidth="1" style="1"/>
-    <col min="13" max="13" width="38.53249740600586" customWidth="1" style="1"/>
+    <col min="13" max="13" width="35.19544219970703" customWidth="1" style="1"/>
     <col min="14" max="14" width="31.09708023071289" customWidth="1" style="1"/>
     <col min="15" max="15" width="24.68001365661621" customWidth="1" style="1"/>
     <col min="16" max="16" width="14.40988826751709" customWidth="1" style="1"/>
@@ -854,37 +800,37 @@
         <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C10" s="7">
-        <v>46139</v>
+        <v>46082</v>
       </c>
       <c r="D10" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E10" s="7">
-        <v>46168</v>
+        <v>46132</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-30</v>
+        <v>-37</v>
       </c>
       <c r="G10" s="8">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>23</v>
@@ -899,33 +845,33 @@
         <v>23</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>32</v>
       </c>
       <c r="S10" s="9">
-        <v>650</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7">
         <v>46140</v>
       </c>
       <c r="C11" s="7">
-        <v>46082</v>
+        <v>46118</v>
       </c>
       <c r="D11" s="7">
-        <v>46132</v>
+        <v>46111</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-37</v>
+        <v>-58</v>
       </c>
       <c r="G11" s="8">
         <v>-29</v>
@@ -937,7 +883,7 @@
         <v>33</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>23</v>
@@ -964,27 +910,27 @@
         <v>32</v>
       </c>
       <c r="S11" s="9">
-        <v>104.04</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>46140</v>
       </c>
       <c r="C12" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="D12" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-58</v>
+        <v>-44</v>
       </c>
       <c r="G12" s="8">
         <v>-29</v>
@@ -996,7 +942,7 @@
         <v>33</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
@@ -1023,7 +969,7 @@
         <v>32</v>
       </c>
       <c r="S12" s="9">
-        <v>275.41</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1031,38 +977,38 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C13" s="7">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="D13" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-44</v>
+        <v>-19</v>
       </c>
       <c r="G13" s="8">
-        <v>-29</v>
+        <v>-23</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="M13" s="6" t="s">
         <v>23</v>
       </c>
@@ -1076,13 +1022,13 @@
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="S13" s="9">
-        <v>408.24</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1093,16 +1039,16 @@
         <v>46146</v>
       </c>
       <c r="C14" s="7">
-        <v>46113</v>
+        <v>46146</v>
       </c>
       <c r="D14" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46141</v>
+        <v>46146</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F14" s="8">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="G14" s="8">
         <v>-23</v>
@@ -1114,13 +1060,13 @@
         <v>33</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>23</v>
@@ -1135,13 +1081,13 @@
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="S14" s="9">
-        <v>12.9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1152,16 +1098,16 @@
         <v>46146</v>
       </c>
       <c r="C15" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D15" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E15" s="7">
+        <v>46097</v>
       </c>
       <c r="F15" s="8">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="G15" s="8">
         <v>-23</v>
@@ -1173,16 +1119,16 @@
         <v>33</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1194,13 +1140,13 @@
         <v>23</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S15" s="9">
-        <v>61.21</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1208,22 +1154,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C16" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D16" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46148</v>
       </c>
       <c r="F16" s="8">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="G16" s="8">
-        <v>-23</v>
+        <v>-20</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>33</v>
@@ -1232,13 +1178,13 @@
         <v>33</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1253,13 +1199,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="S16" s="9">
-        <v>120</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1267,37 +1213,37 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C17" s="7">
-        <v>46082</v>
+        <v>46125</v>
       </c>
       <c r="D17" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46097</v>
+        <v>46125</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-23</v>
+        <v>-44</v>
       </c>
       <c r="G17" s="8">
-        <v>-23</v>
+        <v>-19</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1312,13 +1258,13 @@
         <v>23</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S17" s="9">
-        <v>146.55</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1326,22 +1272,22 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C18" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D18" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E18" s="7">
-        <v>46168</v>
+        <v>46097</v>
       </c>
       <c r="F18" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="G18" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>33</v>
@@ -1350,13 +1296,13 @@
         <v>33</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
@@ -1371,13 +1317,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>32</v>
       </c>
       <c r="S18" s="9">
-        <v>650</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1385,22 +1331,22 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="C19" s="7">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="D19" s="7">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="E19" s="7">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="F19" s="8">
-        <v>-27</v>
+        <v>-16</v>
       </c>
       <c r="G19" s="8">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>33</v>
@@ -1433,10 +1379,10 @@
         <v>35</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="S19" s="9">
-        <v>685.71</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1444,37 +1390,37 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C20" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="D20" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E20" s="7">
+        <v>46119</v>
       </c>
       <c r="F20" s="8">
-        <v>-44</v>
+        <v>-16</v>
       </c>
       <c r="G20" s="8">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1489,13 +1435,13 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S20" s="9">
-        <v>53.82</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1503,22 +1449,22 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C21" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D21" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46097</v>
+        <v>46160</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G21" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>33</v>
@@ -1527,13 +1473,13 @@
         <v>33</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1548,13 +1494,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S21" s="9">
-        <v>146.55</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1562,22 +1508,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C22" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D22" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E22" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G22" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>33</v>
@@ -1586,13 +1532,13 @@
         <v>33</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
@@ -1607,13 +1553,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S22" s="9">
-        <v>310</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1621,22 +1567,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C23" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D23" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E23" s="7">
-        <v>46168</v>
+        <v>46127</v>
       </c>
       <c r="F23" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>33</v>
@@ -1645,16 +1591,16 @@
         <v>33</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1669,10 +1615,10 @@
         <v>35</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S23" s="9">
-        <v>650</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1680,22 +1626,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C24" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D24" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E24" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>33</v>
@@ -1704,13 +1650,13 @@
         <v>33</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1728,10 +1674,10 @@
         <v>35</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S24" s="9">
-        <v>680</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1739,22 +1685,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C25" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D25" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E25" s="7">
+        <v>46119</v>
       </c>
       <c r="F25" s="8">
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>33</v>
@@ -1763,16 +1709,16 @@
         <v>33</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1784,13 +1730,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>280</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1798,22 +1744,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C26" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D26" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46119</v>
       </c>
       <c r="F26" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="8">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>33</v>
@@ -1822,13 +1768,13 @@
         <v>33</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1843,13 +1789,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S26" s="9">
-        <v>530</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1865,8 +1811,8 @@
       <c r="D27" s="7">
         <v>46160</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>23</v>
+      <c r="E27" s="7">
+        <v>46119</v>
       </c>
       <c r="F27" s="8">
         <v>-9</v>
@@ -1881,13 +1827,13 @@
         <v>33</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1899,16 +1845,16 @@
         <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>97.5</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1916,22 +1862,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C28" s="7">
-        <v>46082</v>
+        <v>46146</v>
       </c>
       <c r="D28" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46097</v>
+        <v>46146</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>33</v>
@@ -1940,16 +1886,16 @@
         <v>33</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -1961,13 +1907,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>146.55</v>
+        <v>179.12</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -1975,22 +1921,22 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C29" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D29" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E29" s="7">
-        <v>46127</v>
+        <v>46146</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G29" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>33</v>
@@ -1999,16 +1945,16 @@
         <v>33</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2020,13 +1966,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>172</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2034,7 +1980,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C30" s="7">
         <v>46160</v>
@@ -2042,14 +1988,14 @@
       <c r="D30" s="7">
         <v>46160</v>
       </c>
-      <c r="E30" s="7">
-        <v>46141</v>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
         <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>33</v>
@@ -2064,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2079,13 +2025,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>310</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2093,25 +2039,25 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="C31" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D31" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-37</v>
+        <v>-23</v>
       </c>
       <c r="G31" s="8">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>33</v>
@@ -2123,7 +2069,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2141,10 +2087,10 @@
         <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>350</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2152,22 +2098,22 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C32" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D32" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E32" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>33</v>
@@ -2182,10 +2128,10 @@
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2194,16 +2140,16 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>600</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2211,7 +2157,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C33" s="7">
         <v>46160</v>
@@ -2219,14 +2165,14 @@
       <c r="D33" s="7">
         <v>46160</v>
       </c>
-      <c r="E33" s="7">
-        <v>46141</v>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
         <v>-9</v>
       </c>
       <c r="G33" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>33</v>
@@ -2235,16 +2181,16 @@
         <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="M33" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2256,13 +2202,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>620</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2270,7 +2216,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C34" s="7">
         <v>46160</v>
@@ -2278,14 +2224,14 @@
       <c r="D34" s="7">
         <v>46160</v>
       </c>
-      <c r="E34" s="7">
-        <v>46150</v>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
         <v>-9</v>
       </c>
       <c r="G34" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>33</v>
@@ -2294,14 +2240,14 @@
         <v>33</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
       </c>
@@ -2315,13 +2261,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>630</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2329,22 +2275,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C35" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D35" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E35" s="7">
-        <v>46168</v>
+        <v>46097</v>
       </c>
       <c r="F35" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G35" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>33</v>
@@ -2353,13 +2299,13 @@
         <v>33</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2374,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>32</v>
       </c>
       <c r="S35" s="9">
-        <v>650</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2388,22 +2334,22 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C36" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D36" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E36" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F36" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G36" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>33</v>
@@ -2412,13 +2358,13 @@
         <v>33</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2436,10 +2382,10 @@
         <v>35</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>680</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2447,22 +2393,22 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C37" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D37" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>33</v>
@@ -2471,16 +2417,16 @@
         <v>33</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2489,16 +2435,16 @@
         <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2506,22 +2452,22 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="C38" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D38" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-30</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="8">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>33</v>
@@ -2530,7 +2476,7 @@
         <v>33</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
@@ -2548,7 +2494,7 @@
         <v>27</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>23</v>
@@ -2557,7 +2503,7 @@
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>50</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2565,22 +2511,22 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="C39" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D39" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46119</v>
       </c>
       <c r="F39" s="8">
-        <v>-23</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="8">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>33</v>
@@ -2589,16 +2535,16 @@
         <v>33</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2610,13 +2556,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>179.12</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2624,40 +2570,40 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C40" s="7">
-        <v>46125</v>
+        <v>46167</v>
       </c>
       <c r="D40" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46141</v>
       </c>
       <c r="F40" s="8">
-        <v>-44</v>
+        <v>-2</v>
       </c>
       <c r="G40" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2669,13 +2615,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>50</v>
+        <v>620</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2683,22 +2629,22 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C41" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D41" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46169</v>
       </c>
       <c r="F41" s="8">
-        <v>-23</v>
+        <v>-2</v>
       </c>
       <c r="G41" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>33</v>
@@ -2707,16 +2653,16 @@
         <v>33</v>
       </c>
       <c r="J41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="M41" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2728,13 +2674,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2742,22 +2688,22 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C42" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D42" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46150</v>
       </c>
       <c r="F42" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G42" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>33</v>
@@ -2772,7 +2718,7 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2787,13 +2733,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>380</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2801,22 +2747,22 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C43" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D43" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46163</v>
       </c>
       <c r="F43" s="8">
-        <v>-23</v>
+        <v>-2</v>
       </c>
       <c r="G43" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>33</v>
@@ -2825,13 +2771,13 @@
         <v>33</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2846,13 +2792,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2863,16 +2809,16 @@
         <v>46167</v>
       </c>
       <c r="C44" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D44" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46168</v>
       </c>
       <c r="F44" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G44" s="8">
         <v>-2</v>
@@ -2884,13 +2830,13 @@
         <v>33</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -2905,13 +2851,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S44" s="9">
-        <v>140</v>
+        <v>650</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -2922,13 +2868,13 @@
         <v>46167</v>
       </c>
       <c r="C45" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D45" s="7">
         <v>46167</v>
       </c>
       <c r="E45" s="7">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="F45" s="8">
         <v>-2</v>
@@ -2943,16 +2889,16 @@
         <v>33</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -2964,13 +2910,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S45" s="9">
-        <v>146.55</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -2981,16 +2927,16 @@
         <v>46167</v>
       </c>
       <c r="C46" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D46" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46119</v>
       </c>
       <c r="F46" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="8">
         <v>-2</v>
@@ -3002,13 +2948,13 @@
         <v>33</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3023,13 +2969,13 @@
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S46" s="9">
-        <v>210.87</v>
+        <v>680</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3046,7 +2992,7 @@
         <v>46167</v>
       </c>
       <c r="E47" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F47" s="8">
         <v>-2</v>
@@ -3061,13 +3007,13 @@
         <v>33</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3085,10 +3031,10 @@
         <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S47" s="9">
-        <v>310</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3099,16 +3045,16 @@
         <v>46167</v>
       </c>
       <c r="C48" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D48" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46168</v>
       </c>
       <c r="F48" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G48" s="8">
         <v>-2</v>
@@ -3120,16 +3066,16 @@
         <v>33</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3141,13 +3087,13 @@
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>337.36</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3163,8 +3109,8 @@
       <c r="D49" s="7">
         <v>46167</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>23</v>
+      <c r="E49" s="7">
+        <v>46141</v>
       </c>
       <c r="F49" s="8">
         <v>-2</v>
@@ -3179,13 +3125,13 @@
         <v>33</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3200,13 +3146,13 @@
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S49" s="9">
-        <v>350</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3217,16 +3163,16 @@
         <v>46167</v>
       </c>
       <c r="C50" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D50" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46167</v>
       </c>
       <c r="F50" s="8">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="8">
         <v>-2</v>
@@ -3238,16 +3184,16 @@
         <v>33</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
@@ -3259,33 +3205,33 @@
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>400</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="B51" s="7">
         <v>46167</v>
       </c>
       <c r="C51" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D51" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46129</v>
       </c>
       <c r="F51" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G51" s="8">
         <v>-2</v>
@@ -3297,13 +3243,13 @@
         <v>33</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3318,957 +3264,72 @@
         <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S51" s="9">
-        <v>572.72</v>
+        <v>800</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
-      <c r="A52" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C52" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D52" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E52" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R52" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S52" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="53" ht="23" customHeight="1">
-      <c r="A53" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C53" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D53" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E53" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F53" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R53" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S53" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="54" ht="23" customHeight="1">
-      <c r="A54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B54" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C54" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D54" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F54" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G54" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q54" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R54" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S54" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="55" ht="23" customHeight="1">
-      <c r="A55" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C55" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D55" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F55" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G55" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R55" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S55" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="56" ht="23" customHeight="1">
-      <c r="A56" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B56" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C56" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D56" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46163</v>
-      </c>
-      <c r="F56" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q56" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R56" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S56" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="57" ht="23" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B57" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C57" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D57" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E57" s="7">
-        <v>46150</v>
-      </c>
-      <c r="F57" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G57" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O57" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q57" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S57" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="58" ht="23" customHeight="1">
-      <c r="A58" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C58" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D58" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E58" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q58" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R58" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S58" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="59" ht="23" customHeight="1">
-      <c r="A59" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C59" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D59" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E59" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F59" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G59" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N59" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O59" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R59" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S59" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="60" ht="23" customHeight="1">
-      <c r="A60" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C60" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D60" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F60" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G60" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S60" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="61" ht="23" customHeight="1">
-      <c r="A61" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B61" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C61" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D61" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E61" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F61" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G61" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q61" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R61" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S61" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="62" ht="23" customHeight="1">
-      <c r="A62" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C62" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D62" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E62" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F62" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G62" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q62" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R62" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S62" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="63" ht="23" customHeight="1">
-      <c r="A63" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C63" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D63" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E63" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F63" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="M63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N63" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R63" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S63" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="64" ht="23" customHeight="1">
-      <c r="A64" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B64" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C64" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D64" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E64" s="7">
-        <v>46164</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G64" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q64" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R64" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S64" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="65" ht="23" customHeight="1">
-      <c r="A65" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B65" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C65" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D65" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E65" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F65" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G65" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N65" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O65" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q65" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R65" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S65" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="66" ht="23" customHeight="1">
-      <c r="A66" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B66" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C66" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D66" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E66" s="7">
-        <v>46129</v>
-      </c>
-      <c r="F66" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G66" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q66" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S66" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="67" ht="23" customHeight="1">
-      <c r="A67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R67" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S67" s="13">
-        <f>SUM(S6:S66)</f>
+      <c r="A52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S52" s="13">
+        <f>SUM(S6:S51)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$45</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -196,30 +196,27 @@
     <t>FA-11559</t>
   </si>
   <si>
-    <t>FA-11474</t>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
   </si>
   <si>
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
     <t>FA-11690</t>
   </si>
   <si>
@@ -268,15 +265,15 @@
     <t>JONILSON JOSEMAR DO NASCIMENTO</t>
   </si>
   <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
     <t>FA-11617</t>
   </si>
   <si>
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
     <t>FA-11709</t>
   </si>
   <si>
@@ -286,28 +283,28 @@
     <t>FA-11412</t>
   </si>
   <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11710</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11691</t>
+  </si>
+  <si>
     <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11676</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11710</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11691</t>
   </si>
   <si>
     <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
@@ -459,7 +456,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -1715,10 +1712,10 @@
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1733,10 +1730,10 @@
         <v>35</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S25" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1768,14 +1765,14 @@
         <v>33</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
       </c>
@@ -1786,16 +1783,16 @@
         <v>27</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S26" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1803,22 +1800,22 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C27" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D27" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>33</v>
@@ -1836,7 +1833,7 @@
         <v>58</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -1845,16 +1842,16 @@
         <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>700</v>
+        <v>179.12</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1862,7 +1859,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C28" s="7">
         <v>46146</v>
@@ -1877,7 +1874,7 @@
         <v>-23</v>
       </c>
       <c r="G28" s="8">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>33</v>
@@ -1913,7 +1910,7 @@
         <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>179.12</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -1924,16 +1921,16 @@
         <v>46162</v>
       </c>
       <c r="C29" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D29" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="G29" s="8">
         <v>-7</v>
@@ -1951,10 +1948,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -1972,7 +1969,7 @@
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>200</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -1980,22 +1977,22 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C30" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D30" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G30" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>33</v>
@@ -2010,7 +2007,7 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2031,7 +2028,7 @@
         <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>380</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2039,22 +2036,22 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C31" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D31" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="G31" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>33</v>
@@ -2069,7 +2066,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2081,7 +2078,7 @@
         <v>27</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>23</v>
@@ -2090,7 +2087,7 @@
         <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>210</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2101,16 +2098,16 @@
         <v>46167</v>
       </c>
       <c r="C32" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D32" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="8">
         <v>-2</v>
@@ -2128,10 +2125,10 @@
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2140,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>23</v>
@@ -2149,7 +2146,7 @@
         <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>50</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2181,16 +2178,16 @@
         <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2208,7 +2205,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>61.21</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2219,16 +2216,16 @@
         <v>46167</v>
       </c>
       <c r="C34" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D34" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46097</v>
       </c>
       <c r="F34" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G34" s="8">
         <v>-2</v>
@@ -2240,13 +2237,13 @@
         <v>33</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2261,13 +2258,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S34" s="9">
-        <v>140</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2278,13 +2275,13 @@
         <v>46167</v>
       </c>
       <c r="C35" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D35" s="7">
         <v>46167</v>
       </c>
       <c r="E35" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F35" s="8">
         <v>-2</v>
@@ -2299,13 +2296,13 @@
         <v>33</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2320,13 +2317,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2337,16 +2334,16 @@
         <v>46167</v>
       </c>
       <c r="C36" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D36" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46141</v>
+        <v>46153</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="G36" s="8">
         <v>-2</v>
@@ -2364,10 +2361,10 @@
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2379,13 +2376,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>310</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2396,16 +2393,16 @@
         <v>46167</v>
       </c>
       <c r="C37" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D37" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G37" s="8">
         <v>-2</v>
@@ -2423,10 +2420,10 @@
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2444,7 +2441,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>400</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2455,16 +2452,16 @@
         <v>46167</v>
       </c>
       <c r="C38" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D38" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46119</v>
       </c>
       <c r="F38" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="8">
         <v>-2</v>
@@ -2476,16 +2473,16 @@
         <v>33</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2497,13 +2494,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>572.72</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2520,7 +2517,7 @@
         <v>46167</v>
       </c>
       <c r="E39" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F39" s="8">
         <v>-2</v>
@@ -2541,10 +2538,10 @@
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2562,7 +2559,7 @@
         <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2579,7 +2576,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F40" s="8">
         <v>-2</v>
@@ -2594,16 +2591,16 @@
         <v>33</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2621,7 +2618,7 @@
         <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2638,7 +2635,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F41" s="8">
         <v>-2</v>
@@ -2653,13 +2650,13 @@
         <v>33</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2756,7 +2753,7 @@
         <v>46167</v>
       </c>
       <c r="E43" s="7">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="F43" s="8">
         <v>-2</v>
@@ -2777,7 +2774,7 @@
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2795,10 +2792,10 @@
         <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S43" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2815,7 +2812,7 @@
         <v>46167</v>
       </c>
       <c r="E44" s="7">
-        <v>46168</v>
+        <v>46113</v>
       </c>
       <c r="F44" s="8">
         <v>-2</v>
@@ -2830,16 +2827,16 @@
         <v>33</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -2854,10 +2851,10 @@
         <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -2874,7 +2871,7 @@
         <v>46167</v>
       </c>
       <c r="E45" s="7">
-        <v>46113</v>
+        <v>46164</v>
       </c>
       <c r="F45" s="8">
         <v>-2</v>
@@ -2895,10 +2892,10 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -2913,7 +2910,7 @@
         <v>35</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S45" s="9">
         <v>680</v>
@@ -2933,7 +2930,7 @@
         <v>46167</v>
       </c>
       <c r="E46" s="7">
-        <v>46119</v>
+        <v>46168</v>
       </c>
       <c r="F46" s="8">
         <v>-2</v>
@@ -2948,13 +2945,13 @@
         <v>33</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -2972,7 +2969,7 @@
         <v>35</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
         <v>680</v>
@@ -2992,7 +2989,7 @@
         <v>46167</v>
       </c>
       <c r="E47" s="7">
-        <v>46164</v>
+        <v>46141</v>
       </c>
       <c r="F47" s="8">
         <v>-2</v>
@@ -3007,13 +3004,13 @@
         <v>33</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3051,7 +3048,7 @@
         <v>46167</v>
       </c>
       <c r="E48" s="7">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="F48" s="8">
         <v>-2</v>
@@ -3066,13 +3063,13 @@
         <v>33</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3110,7 +3107,7 @@
         <v>46167</v>
       </c>
       <c r="E49" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F49" s="8">
         <v>-2</v>
@@ -3125,13 +3122,13 @@
         <v>33</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3157,7 +3154,7 @@
     </row>
     <row r="50" ht="23" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="B50" s="7">
         <v>46167</v>
@@ -3169,7 +3166,7 @@
         <v>46167</v>
       </c>
       <c r="E50" s="7">
-        <v>46167</v>
+        <v>46129</v>
       </c>
       <c r="F50" s="8">
         <v>-2</v>
@@ -3184,13 +3181,13 @@
         <v>33</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3208,128 +3205,69 @@
         <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S50" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C51" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D51" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E51" s="7">
-        <v>46129</v>
-      </c>
-      <c r="F51" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q51" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="S51" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="52" ht="23" customHeight="1">
-      <c r="A52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S52" s="13">
-        <f>SUM(S6:S51)</f>
+      <c r="A51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S51" s="13">
+        <f>SUM(S6:S50)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -148,9 +148,6 @@
     <t>ATIVUZ VEÍCULOS</t>
   </si>
   <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
     <t>FA-11559</t>
   </si>
   <si>
@@ -205,18 +202,18 @@
     <t>FA-11480</t>
   </si>
   <si>
-    <t>FA-11715</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>FA-11617</t>
   </si>
   <si>
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
+    <t>FA-11773</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
     <t>FA-11676</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
   </si>
 </sst>
 </file>
@@ -384,7 +378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -1020,22 +1014,22 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C15" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D15" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46119</v>
+        <v>46160</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="G15" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>30</v>
@@ -1044,13 +1038,13 @@
         <v>30</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>23</v>
@@ -1065,13 +1059,13 @@
         <v>23</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S15" s="9">
-        <v>680</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1082,13 +1076,13 @@
         <v>46160</v>
       </c>
       <c r="C16" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D16" s="7">
         <v>46160</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
+      <c r="E16" s="7">
+        <v>46097</v>
       </c>
       <c r="F16" s="8">
         <v>-10</v>
@@ -1103,13 +1097,13 @@
         <v>30</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1124,13 +1118,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S16" s="9">
-        <v>97.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1141,13 +1135,13 @@
         <v>46160</v>
       </c>
       <c r="C17" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="7">
         <v>46160</v>
       </c>
       <c r="E17" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F17" s="8">
         <v>-10</v>
@@ -1162,13 +1156,13 @@
         <v>30</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1183,13 +1177,13 @@
         <v>23</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S17" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1206,7 +1200,7 @@
         <v>46160</v>
       </c>
       <c r="E18" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F18" s="8">
         <v>-10</v>
@@ -1227,7 +1221,7 @@
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
@@ -1239,7 +1233,7 @@
         <v>27</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>36</v>
@@ -1248,7 +1242,7 @@
         <v>37</v>
       </c>
       <c r="S18" s="9">
-        <v>310</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1256,22 +1250,22 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C19" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D19" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="G19" s="8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>30</v>
@@ -1280,16 +1274,16 @@
         <v>30</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>27</v>
@@ -1298,16 +1292,16 @@
         <v>27</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S19" s="9">
-        <v>700</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1315,7 +1309,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C20" s="7">
         <v>46146</v>
@@ -1330,7 +1324,7 @@
         <v>-24</v>
       </c>
       <c r="G20" s="8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>30</v>
@@ -1339,16 +1333,16 @@
         <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>27</v>
@@ -1366,7 +1360,7 @@
         <v>37</v>
       </c>
       <c r="S20" s="9">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1374,22 +1368,22 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C21" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D21" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-24</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>30</v>
@@ -1404,7 +1398,7 @@
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1416,7 +1410,7 @@
         <v>27</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>23</v>
@@ -1425,7 +1419,7 @@
         <v>37</v>
       </c>
       <c r="S21" s="9">
-        <v>210</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1436,16 +1430,16 @@
         <v>46167</v>
       </c>
       <c r="C22" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D22" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="8">
         <v>-3</v>
@@ -1463,10 +1457,10 @@
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1475,7 +1469,7 @@
         <v>27</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>23</v>
@@ -1484,7 +1478,7 @@
         <v>37</v>
       </c>
       <c r="S22" s="9">
-        <v>50</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1495,16 +1489,16 @@
         <v>46167</v>
       </c>
       <c r="C23" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D23" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46097</v>
       </c>
       <c r="F23" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G23" s="8">
         <v>-3</v>
@@ -1516,16 +1510,16 @@
         <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1537,13 +1531,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S23" s="9">
-        <v>61.21</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1554,13 +1548,13 @@
         <v>46167</v>
       </c>
       <c r="C24" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D24" s="7">
         <v>46167</v>
       </c>
       <c r="E24" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
         <v>-3</v>
@@ -1575,13 +1569,13 @@
         <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1596,13 +1590,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S24" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1613,16 +1607,16 @@
         <v>46167</v>
       </c>
       <c r="C25" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D25" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46141</v>
+        <v>46153</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="G25" s="8">
         <v>-3</v>
@@ -1640,10 +1634,10 @@
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1655,13 +1649,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S25" s="9">
-        <v>310</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1672,16 +1666,16 @@
         <v>46167</v>
       </c>
       <c r="C26" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D26" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="G26" s="8">
         <v>-3</v>
@@ -1693,16 +1687,16 @@
         <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1720,7 +1714,7 @@
         <v>37</v>
       </c>
       <c r="S26" s="9">
-        <v>400</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1731,16 +1725,16 @@
         <v>46167</v>
       </c>
       <c r="C27" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D27" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="8">
         <v>-3</v>
@@ -1752,13 +1746,13 @@
         <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1776,10 +1770,10 @@
         <v>23</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
-        <v>572.72</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1795,8 +1789,8 @@
       <c r="D28" s="7">
         <v>46167</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+      <c r="E28" s="7">
+        <v>46119</v>
       </c>
       <c r="F28" s="8">
         <v>-3</v>
@@ -1811,16 +1805,16 @@
         <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -1832,10 +1826,10 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S28" s="9">
         <v>600</v>
@@ -1855,7 +1849,7 @@
         <v>46167</v>
       </c>
       <c r="E29" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F29" s="8">
         <v>-3</v>
@@ -1876,10 +1870,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -1897,7 +1891,7 @@
         <v>37</v>
       </c>
       <c r="S29" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -1914,7 +1908,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F30" s="8">
         <v>-3</v>
@@ -1929,16 +1923,16 @@
         <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -1956,7 +1950,7 @@
         <v>37</v>
       </c>
       <c r="S30" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -1973,7 +1967,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="7">
-        <v>46150</v>
+        <v>46113</v>
       </c>
       <c r="F31" s="8">
         <v>-3</v>
@@ -1994,10 +1988,10 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2015,7 +2009,7 @@
         <v>37</v>
       </c>
       <c r="S31" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2047,13 +2041,13 @@
         <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2106,13 +2100,13 @@
         <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2165,13 +2159,13 @@
         <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2224,13 +2218,13 @@
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2255,121 +2249,62 @@
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
-      <c r="A36" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C36" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D36" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S36" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="37" ht="23" customHeight="1">
-      <c r="A37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S37" s="13">
-        <f>SUM(S6:S36)</f>
+      <c r="A36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S36" s="13">
+        <f>SUM(S6:S35)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$78</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,7 +36,7 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 01/06/2026</t>
     </r>
   </si>
   <si>
@@ -224,6 +224,255 @@
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11759</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11486</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11718</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11746</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11780</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11721</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>FA-11719</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11669</t>
+  </si>
+  <si>
+    <t>FA-11754</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11777</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11684</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11793</t>
+  </si>
+  <si>
+    <t>FA-11505</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11622</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11657</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11435</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11567</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>FA-11712</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
+    <t>FA-11413</t>
+  </si>
+  <si>
+    <t>FA-11778</t>
+  </si>
+  <si>
+    <t>FA-11762</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11330</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11602</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11537</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>FA-11633</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11579</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11592</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>FA-11645</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -366,7 +615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -380,13 +629,13 @@
     <col min="9" max="9" width="36.28671646118164" customWidth="1" style="1"/>
     <col min="10" max="10" width="25.261001586914062" customWidth="1" style="1"/>
     <col min="11" max="11" width="15.191652297973633" customWidth="1" style="1"/>
-    <col min="12" max="12" width="43.70395278930664" customWidth="1" style="1"/>
-    <col min="13" max="13" width="35.19544219970703" customWidth="1" style="1"/>
+    <col min="12" max="12" width="45.98413848876953" customWidth="1" style="1"/>
+    <col min="13" max="13" width="38.53249740600586" customWidth="1" style="1"/>
     <col min="14" max="14" width="31.09708023071289" customWidth="1" style="1"/>
     <col min="15" max="15" width="24.68001365661621" customWidth="1" style="1"/>
     <col min="16" max="16" width="14.40988826751709" customWidth="1" style="1"/>
     <col min="17" max="17" width="16.712258338928223" customWidth="1" style="1"/>
-    <col min="18" max="18" width="23.309049606323242" customWidth="1" style="1"/>
+    <col min="18" max="18" width="26.100889205932617" customWidth="1" style="1"/>
     <col min="19" max="19" width="15" customWidth="1" style="1"/>
     <col min="20" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
@@ -2119,62 +2368,3012 @@
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
-      <c r="A34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S34" s="13">
-        <f>SUM(S6:S33)</f>
+      <c r="A34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46168</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D34" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-17</v>
+      </c>
+      <c r="G34" s="8">
+        <v>-2</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S34" s="9">
+        <v>13.43</v>
+      </c>
+    </row>
+    <row r="35" ht="23" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46168</v>
+      </c>
+      <c r="C35" s="7">
+        <v>46132</v>
+      </c>
+      <c r="D35" s="7">
+        <v>46132</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="8">
+        <v>-38</v>
+      </c>
+      <c r="G35" s="8">
+        <v>-2</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S35" s="9">
+        <v>249.21</v>
+      </c>
+    </row>
+    <row r="36" ht="23" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46168</v>
+      </c>
+      <c r="C36" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D36" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G36" s="8">
+        <v>-2</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S36" s="9">
+        <v>262.56</v>
+      </c>
+    </row>
+    <row r="37" ht="23" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46169</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D37" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S37" s="9">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" ht="23" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46169</v>
+      </c>
+      <c r="C38" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D38" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S38" s="9">
+        <v>301.57</v>
+      </c>
+    </row>
+    <row r="39" ht="23" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46169</v>
+      </c>
+      <c r="C39" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D39" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G39" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S39" s="9">
+        <v>306.75</v>
+      </c>
+    </row>
+    <row r="40" ht="23" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46170</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D40" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="8">
+        <v>-24</v>
+      </c>
+      <c r="G40" s="8">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S40" s="9">
+        <v>79.12</v>
+      </c>
+    </row>
+    <row r="41" ht="23" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46170</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D41" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S41" s="9">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" ht="23" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46170</v>
+      </c>
+      <c r="C42" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D42" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="8">
+        <v>-10</v>
+      </c>
+      <c r="G42" s="8">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S42" s="9">
+        <v>233.82</v>
+      </c>
+    </row>
+    <row r="43" ht="23" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46170</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D43" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G43" s="8">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S43" s="9">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="44" ht="23" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46172</v>
+      </c>
+      <c r="C44" s="7">
+        <v>45930</v>
+      </c>
+      <c r="D44" s="7">
+        <v>46172</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="8">
+        <v>2</v>
+      </c>
+      <c r="G44" s="8">
+        <v>2</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S44" s="9">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="45" ht="23" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D45" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F45" s="8">
+        <v>4</v>
+      </c>
+      <c r="G45" s="8">
+        <v>4</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S45" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" ht="23" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D46" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F46" s="8">
+        <v>4</v>
+      </c>
+      <c r="G46" s="8">
+        <v>4</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S46" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" ht="23" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F47" s="8">
+        <v>4</v>
+      </c>
+      <c r="G47" s="8">
+        <v>4</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S47" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="48" ht="23" customHeight="1">
+      <c r="A48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F48" s="8">
+        <v>4</v>
+      </c>
+      <c r="G48" s="8">
+        <v>4</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S48" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" ht="23" customHeight="1">
+      <c r="A49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F49" s="8">
+        <v>4</v>
+      </c>
+      <c r="G49" s="8">
+        <v>4</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S49" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F50" s="8">
+        <v>4</v>
+      </c>
+      <c r="G50" s="8">
+        <v>4</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S50" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" ht="23" customHeight="1">
+      <c r="A51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F51" s="8">
+        <v>4</v>
+      </c>
+      <c r="G51" s="8">
+        <v>4</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S51" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="52" ht="23" customHeight="1">
+      <c r="A52" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F52" s="8">
+        <v>4</v>
+      </c>
+      <c r="G52" s="8">
+        <v>4</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S52" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="53" ht="23" customHeight="1">
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F53" s="8">
+        <v>4</v>
+      </c>
+      <c r="G53" s="8">
+        <v>4</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S53" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="54" ht="23" customHeight="1">
+      <c r="A54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F54" s="8">
+        <v>4</v>
+      </c>
+      <c r="G54" s="8">
+        <v>4</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S54" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="55" ht="23" customHeight="1">
+      <c r="A55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F55" s="8">
+        <v>4</v>
+      </c>
+      <c r="G55" s="8">
+        <v>4</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S55" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="56" ht="23" customHeight="1">
+      <c r="A56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46163</v>
+      </c>
+      <c r="F56" s="8">
+        <v>4</v>
+      </c>
+      <c r="G56" s="8">
+        <v>4</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S56" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="57" ht="23" customHeight="1">
+      <c r="A57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F57" s="8">
+        <v>4</v>
+      </c>
+      <c r="G57" s="8">
+        <v>4</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S57" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="58" ht="23" customHeight="1">
+      <c r="A58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F58" s="8">
+        <v>4</v>
+      </c>
+      <c r="G58" s="8">
+        <v>4</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S58" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="59" ht="23" customHeight="1">
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F59" s="8">
+        <v>4</v>
+      </c>
+      <c r="G59" s="8">
+        <v>4</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S59" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="60" ht="23" customHeight="1">
+      <c r="A60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F60" s="8">
+        <v>4</v>
+      </c>
+      <c r="G60" s="8">
+        <v>4</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S60" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="61" ht="23" customHeight="1">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F61" s="8">
+        <v>4</v>
+      </c>
+      <c r="G61" s="8">
+        <v>4</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S61" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="62" ht="23" customHeight="1">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F62" s="8">
+        <v>4</v>
+      </c>
+      <c r="G62" s="8">
+        <v>4</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S62" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="63" ht="23" customHeight="1">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F63" s="8">
+        <v>4</v>
+      </c>
+      <c r="G63" s="8">
+        <v>4</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S63" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="64" ht="23" customHeight="1">
+      <c r="A64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F64" s="8">
+        <v>4</v>
+      </c>
+      <c r="G64" s="8">
+        <v>4</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S64" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="65" ht="23" customHeight="1">
+      <c r="A65" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F65" s="8">
+        <v>4</v>
+      </c>
+      <c r="G65" s="8">
+        <v>4</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S65" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="66" ht="23" customHeight="1">
+      <c r="A66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F66" s="8">
+        <v>4</v>
+      </c>
+      <c r="G66" s="8">
+        <v>4</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S66" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="67" ht="23" customHeight="1">
+      <c r="A67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F67" s="8">
+        <v>4</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="68" ht="23" customHeight="1">
+      <c r="A68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F68" s="8">
+        <v>4</v>
+      </c>
+      <c r="G68" s="8">
+        <v>4</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S68" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="69" ht="23" customHeight="1">
+      <c r="A69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F69" s="8">
+        <v>4</v>
+      </c>
+      <c r="G69" s="8">
+        <v>4</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S69" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="70" ht="23" customHeight="1">
+      <c r="A70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F70" s="8">
+        <v>4</v>
+      </c>
+      <c r="G70" s="8">
+        <v>4</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S70" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="71" ht="23" customHeight="1">
+      <c r="A71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F71" s="8">
+        <v>4</v>
+      </c>
+      <c r="G71" s="8">
+        <v>4</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S71" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="72" ht="23" customHeight="1">
+      <c r="A72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F72" s="8">
+        <v>4</v>
+      </c>
+      <c r="G72" s="8">
+        <v>4</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S72" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="73" ht="23" customHeight="1">
+      <c r="A73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F73" s="8">
+        <v>4</v>
+      </c>
+      <c r="G73" s="8">
+        <v>4</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S73" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="74" ht="23" customHeight="1">
+      <c r="A74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F74" s="8">
+        <v>4</v>
+      </c>
+      <c r="G74" s="8">
+        <v>4</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S74" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="75" ht="23" customHeight="1">
+      <c r="A75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F75" s="8">
+        <v>4</v>
+      </c>
+      <c r="G75" s="8">
+        <v>4</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q75" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S75" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="76" ht="23" customHeight="1">
+      <c r="A76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F76" s="8">
+        <v>4</v>
+      </c>
+      <c r="G76" s="8">
+        <v>4</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S76" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="77" ht="23" customHeight="1">
+      <c r="A77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F77" s="8">
+        <v>4</v>
+      </c>
+      <c r="G77" s="8">
+        <v>4</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q77" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S77" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="78" ht="23" customHeight="1">
+      <c r="A78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F78" s="8">
+        <v>4</v>
+      </c>
+      <c r="G78" s="8">
+        <v>4</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S78" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="79" ht="23" customHeight="1">
+      <c r="A79" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46129</v>
+      </c>
+      <c r="F79" s="8">
+        <v>4</v>
+      </c>
+      <c r="G79" s="8">
+        <v>4</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S79" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="80" ht="23" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F80" s="8">
+        <v>4</v>
+      </c>
+      <c r="G80" s="8">
+        <v>4</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="S80" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="81" ht="23" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F81" s="8">
+        <v>4</v>
+      </c>
+      <c r="G81" s="8">
+        <v>4</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="S81" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="82" ht="23" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F82" s="8">
+        <v>4</v>
+      </c>
+      <c r="G82" s="8">
+        <v>4</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="S82" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="83" ht="23" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F83" s="8">
+        <v>4</v>
+      </c>
+      <c r="G83" s="8">
+        <v>4</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="S83" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S84" s="13">
+        <f>SUM(S6:S83)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -166,6 +166,9 @@
     <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
   </si>
   <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
     <t>FA-11562</t>
   </si>
   <si>
@@ -229,12 +232,6 @@
     <t>FA-11615</t>
   </si>
   <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
     <t>FA-11489</t>
   </si>
   <si>
@@ -298,28 +295,31 @@
     <t>ND-11700</t>
   </si>
   <si>
+    <t>FA-11746</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11780</t>
+  </si>
+  <si>
     <t>FA-11718</t>
   </si>
   <si>
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
-    <t>FA-11746</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11780</t>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
   </si>
   <si>
     <t>FA-11565</t>
   </si>
   <si>
-    <t>FA-11566</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
+    <t>FA-11669</t>
   </si>
   <si>
     <t>FA-11721</t>
@@ -337,9 +337,6 @@
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11669</t>
-  </si>
-  <si>
     <t>FA-11754</t>
   </si>
   <si>
@@ -373,24 +370,27 @@
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
+    <t>FA-11657</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
     <t>FA-11711</t>
   </si>
   <si>
     <t>FA-11774</t>
   </si>
   <si>
-    <t>FA-11657</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
     <t>FA-11435</t>
   </si>
   <si>
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11413</t>
+  </si>
+  <si>
     <t>FA-11567</t>
   </si>
   <si>
@@ -400,18 +400,15 @@
     <t>FA-11677</t>
   </si>
   <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
     <t>FA-11712</t>
   </si>
   <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>FA-11760</t>
-  </si>
-  <si>
-    <t>FA-11413</t>
-  </si>
-  <si>
     <t>FA-11778</t>
   </si>
   <si>
@@ -445,34 +442,34 @@
     <t>ELIONILSON CORDEIRO BARBOSA</t>
   </si>
   <si>
+    <t>FA-11579</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11592</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>FA-11645</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11633</t>
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11579</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11592</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>FA-11645</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -1672,8 +1669,8 @@
       <c r="D22" s="7">
         <v>46167</v>
       </c>
-      <c r="E22" s="7">
-        <v>46141</v>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F22" s="8">
         <v>-3</v>
@@ -1688,14 +1685,14 @@
         <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
       </c>
@@ -1709,13 +1706,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S22" s="9">
-        <v>310</v>
+        <v>249.21</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1726,16 +1723,16 @@
         <v>46167</v>
       </c>
       <c r="C23" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D23" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46141</v>
       </c>
       <c r="F23" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G23" s="8">
         <v>-3</v>
@@ -1753,10 +1750,10 @@
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1768,13 +1765,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S23" s="9">
-        <v>400</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1785,16 +1782,16 @@
         <v>46167</v>
       </c>
       <c r="C24" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D24" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="G24" s="8">
         <v>-3</v>
@@ -1806,16 +1803,16 @@
         <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1833,7 +1830,7 @@
         <v>37</v>
       </c>
       <c r="S24" s="9">
-        <v>572.72</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1844,16 +1841,16 @@
         <v>46167</v>
       </c>
       <c r="C25" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D25" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
         <v>-3</v>
@@ -1865,14 +1862,14 @@
         <v>30</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1889,10 +1886,10 @@
         <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S25" s="9">
-        <v>600</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1908,8 +1905,8 @@
       <c r="D26" s="7">
         <v>46167</v>
       </c>
-      <c r="E26" s="7">
-        <v>46119</v>
+      <c r="E26" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F26" s="8">
         <v>-3</v>
@@ -1924,16 +1921,16 @@
         <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="M26" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1945,10 +1942,10 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S26" s="9">
         <v>600</v>
@@ -1968,7 +1965,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F27" s="8">
         <v>-3</v>
@@ -1989,10 +1986,10 @@
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -2010,7 +2007,7 @@
         <v>37</v>
       </c>
       <c r="S27" s="9">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2027,7 +2024,7 @@
         <v>46167</v>
       </c>
       <c r="E28" s="7">
-        <v>46170</v>
+        <v>46150</v>
       </c>
       <c r="F28" s="8">
         <v>-3</v>
@@ -2042,16 +2039,16 @@
         <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2069,7 +2066,7 @@
         <v>37</v>
       </c>
       <c r="S28" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2086,7 +2083,7 @@
         <v>46167</v>
       </c>
       <c r="E29" s="7">
-        <v>46113</v>
+        <v>46170</v>
       </c>
       <c r="F29" s="8">
         <v>-3</v>
@@ -2107,10 +2104,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2128,7 +2125,7 @@
         <v>37</v>
       </c>
       <c r="S29" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2145,7 +2142,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="7">
-        <v>46164</v>
+        <v>46113</v>
       </c>
       <c r="F30" s="8">
         <v>-3</v>
@@ -2166,10 +2163,10 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2184,7 +2181,7 @@
         <v>36</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S30" s="9">
         <v>680</v>
@@ -2204,7 +2201,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="7">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="F31" s="8">
         <v>-3</v>
@@ -2219,13 +2216,13 @@
         <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2243,7 +2240,7 @@
         <v>36</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S31" s="9">
         <v>680</v>
@@ -2263,7 +2260,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="7">
-        <v>46141</v>
+        <v>46168</v>
       </c>
       <c r="F32" s="8">
         <v>-3</v>
@@ -2278,13 +2275,13 @@
         <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2302,7 +2299,7 @@
         <v>36</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S32" s="9">
         <v>680</v>
@@ -2322,7 +2319,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="7">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="F33" s="8">
         <v>-3</v>
@@ -2337,13 +2334,13 @@
         <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2361,7 +2358,7 @@
         <v>36</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S33" s="9">
         <v>680</v>
@@ -2372,22 +2369,22 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C34" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D34" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46167</v>
       </c>
       <c r="F34" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>30</v>
@@ -2396,14 +2393,14 @@
         <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
       </c>
@@ -2417,13 +2414,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S34" s="9">
-        <v>13.43</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2434,22 +2431,22 @@
         <v>46168</v>
       </c>
       <c r="C35" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-38</v>
+        <v>-17</v>
       </c>
       <c r="G35" s="8">
         <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>30</v>
@@ -2461,7 +2458,7 @@
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2482,7 +2479,7 @@
         <v>37</v>
       </c>
       <c r="S35" s="9">
-        <v>249.21</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2514,13 +2511,13 @@
         <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2573,13 +2570,13 @@
         <v>30</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2632,13 +2629,13 @@
         <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2691,16 +2688,16 @@
         <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="M39" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2750,22 +2747,22 @@
         <v>23</v>
       </c>
       <c r="J40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
@@ -2809,25 +2806,25 @@
         <v>23</v>
       </c>
       <c r="J41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="6" t="s">
+      <c r="M41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="P41" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P41" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>23</v>
@@ -2868,13 +2865,13 @@
         <v>23</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2883,7 +2880,7 @@
         <v>27</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
@@ -2927,14 +2924,14 @@
         <v>23</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
       </c>
@@ -2942,7 +2939,7 @@
         <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
@@ -2992,16 +2989,16 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -3045,25 +3042,25 @@
         <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K45" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>29</v>
@@ -3104,22 +3101,22 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
@@ -3175,10 +3172,10 @@
         <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
@@ -3222,22 +3219,22 @@
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="K48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="M48" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
@@ -3266,7 +3263,7 @@
         <v>46174</v>
       </c>
       <c r="E49" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F49" s="8">
         <v>4</v>
@@ -3281,22 +3278,22 @@
         <v>23</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
@@ -3325,7 +3322,7 @@
         <v>46174</v>
       </c>
       <c r="E50" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F50" s="8">
         <v>4</v>
@@ -3340,22 +3337,22 @@
         <v>23</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3399,22 +3396,22 @@
         <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="K51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3464,16 +3461,16 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
@@ -3502,7 +3499,7 @@
         <v>46174</v>
       </c>
       <c r="E53" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F53" s="8">
         <v>4</v>
@@ -3517,22 +3514,22 @@
         <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3576,22 +3573,22 @@
         <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3635,22 +3632,22 @@
         <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3679,7 +3676,7 @@
         <v>46174</v>
       </c>
       <c r="E56" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F56" s="8">
         <v>4</v>
@@ -3694,22 +3691,22 @@
         <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3753,22 +3750,22 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3812,25 +3809,25 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>36</v>
@@ -3871,22 +3868,22 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3930,22 +3927,22 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -3989,22 +3986,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4048,22 +4045,22 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4107,22 +4104,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="K63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4151,7 +4148,7 @@
         <v>46174</v>
       </c>
       <c r="E64" s="7">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="F64" s="8">
         <v>4</v>
@@ -4166,22 +4163,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4190,7 +4187,7 @@
         <v>36</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S64" s="9">
         <v>650</v>
@@ -4210,7 +4207,7 @@
         <v>46174</v>
       </c>
       <c r="E65" s="7">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="F65" s="8">
         <v>4</v>
@@ -4231,16 +4228,16 @@
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4249,7 +4246,7 @@
         <v>36</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S65" s="9">
         <v>650</v>
@@ -4269,7 +4266,7 @@
         <v>46174</v>
       </c>
       <c r="E66" s="7">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="F66" s="8">
         <v>4</v>
@@ -4290,16 +4287,16 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4343,22 +4340,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4387,7 +4384,7 @@
         <v>46174</v>
       </c>
       <c r="E68" s="7">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="F68" s="8">
         <v>4</v>
@@ -4402,22 +4399,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4426,7 +4423,7 @@
         <v>36</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S68" s="9">
         <v>680</v>
@@ -4446,7 +4443,7 @@
         <v>46174</v>
       </c>
       <c r="E69" s="7">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="F69" s="8">
         <v>4</v>
@@ -4461,22 +4458,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4485,7 +4482,7 @@
         <v>36</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S69" s="9">
         <v>680</v>
@@ -4505,7 +4502,7 @@
         <v>46174</v>
       </c>
       <c r="E70" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F70" s="8">
         <v>4</v>
@@ -4520,22 +4517,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4544,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S70" s="9">
         <v>680</v>
@@ -4564,7 +4561,7 @@
         <v>46174</v>
       </c>
       <c r="E71" s="7">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="F71" s="8">
         <v>4</v>
@@ -4579,22 +4576,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4603,7 +4600,7 @@
         <v>36</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S71" s="9">
         <v>680</v>
@@ -4638,22 +4635,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4697,22 +4694,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4741,7 +4738,7 @@
         <v>46174</v>
       </c>
       <c r="E74" s="7">
-        <v>46113</v>
+        <v>46168</v>
       </c>
       <c r="F74" s="8">
         <v>4</v>
@@ -4756,22 +4753,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4815,25 +4812,25 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P75" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="M75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N75" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O75" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="P75" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>36</v>
@@ -4874,22 +4871,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4933,22 +4930,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="K77" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L77" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4992,22 +4989,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="K78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5016,7 +5013,7 @@
         <v>36</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S78" s="9">
         <v>800</v>
@@ -5024,7 +5021,7 @@
     </row>
     <row r="79" ht="23" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B79" s="7">
         <v>46174</v>
@@ -5051,22 +5048,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5075,7 +5072,7 @@
         <v>36</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S79" s="9">
         <v>800</v>
@@ -5095,7 +5092,7 @@
         <v>46174</v>
       </c>
       <c r="E80" s="7">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="F80" s="8">
         <v>4</v>
@@ -5110,31 +5107,31 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="K80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="Q80" s="6" t="s">
         <v>36</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S80" s="9">
         <v>1200</v>
@@ -5169,22 +5166,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5193,7 +5190,7 @@
         <v>36</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S81" s="9">
         <v>1200</v>
@@ -5213,7 +5210,7 @@
         <v>46174</v>
       </c>
       <c r="E82" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F82" s="8">
         <v>4</v>
@@ -5228,31 +5225,31 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>36</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S82" s="9">
         <v>1200</v>
@@ -5287,31 +5284,31 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="K83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>36</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S83" s="9">
         <v>1200</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$79</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 01/06/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em Sunday, May 31, 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em Monday, June 1, 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -172,16 +172,103 @@
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11773</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11691</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11759</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11486</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
     <t>FA-11473</t>
   </si>
   <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
     <t>FA-11709</t>
@@ -190,85 +277,184 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11773</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11676</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11691</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11759</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11486</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+    <t>FA-11718</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11780</t>
+  </si>
+  <si>
+    <t>FA-11746</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11721</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>FA-11719</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11669</t>
+  </si>
+  <si>
+    <t>FA-11777</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11684</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11754</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11505</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11622</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11657</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11435</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11567</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>FA-11712</t>
+  </si>
+  <si>
+    <t>FA-11413</t>
+  </si>
+  <si>
+    <t>FA-11778</t>
+  </si>
+  <si>
+    <t>FA-11330</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11762</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11537</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11602</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
+  </si>
+  <si>
+    <t>FA-11645</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11633</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11579</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11592</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
   </si>
 </sst>
 </file>
@@ -411,7 +597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -431,7 +617,7 @@
     <col min="15" max="15" width="26" customWidth="1" style="1"/>
     <col min="16" max="16" width="14" customWidth="1" style="1"/>
     <col min="17" max="17" width="16" customWidth="1" style="1"/>
-    <col min="18" max="18" width="20" customWidth="1" style="1"/>
+    <col min="18" max="18" width="23" customWidth="1" style="1"/>
     <col min="19" max="19" width="16" customWidth="1" style="1"/>
     <col min="20" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
@@ -528,10 +714,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="G6" s="8">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -587,10 +773,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="G7" s="8">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -646,10 +832,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="G8" s="8">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -705,10 +891,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="G9" s="8">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -764,10 +950,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="G10" s="8">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -814,19 +1000,19 @@
         <v>46146</v>
       </c>
       <c r="C11" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D11" s="7">
         <v>46146</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>23</v>
+      <c r="E11" s="7">
+        <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="G11" s="8">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>33</v>
@@ -835,13 +1021,13 @@
         <v>33</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>23</v>
@@ -856,13 +1042,13 @@
         <v>23</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S11" s="9">
-        <v>120</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="12">
@@ -870,22 +1056,22 @@
         <v>22</v>
       </c>
       <c r="B12" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C12" s="7">
         <v>46082</v>
       </c>
       <c r="D12" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E12" s="7">
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="G12" s="8">
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>33</v>
@@ -932,19 +1118,19 @@
         <v>46153</v>
       </c>
       <c r="C13" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D13" s="7">
         <v>46153</v>
       </c>
       <c r="E13" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="G13" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>33</v>
@@ -953,13 +1139,13 @@
         <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>23</v>
@@ -974,13 +1160,13 @@
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S13" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14">
@@ -988,22 +1174,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C14" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D14" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E14" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G14" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>33</v>
@@ -1012,13 +1198,13 @@
         <v>33</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>23</v>
@@ -1033,13 +1219,13 @@
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S14" s="9">
-        <v>310</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="15">
@@ -1050,19 +1236,19 @@
         <v>46160</v>
       </c>
       <c r="C15" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D15" s="7">
         <v>46160</v>
       </c>
       <c r="E15" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G15" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>33</v>
@@ -1071,13 +1257,13 @@
         <v>33</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>23</v>
@@ -1092,13 +1278,13 @@
         <v>23</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S15" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16">
@@ -1106,22 +1292,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="C16" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D16" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46141</v>
+        <v>46146</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-13</v>
+        <v>-28</v>
       </c>
       <c r="G16" s="8">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>33</v>
@@ -1130,7 +1316,7 @@
         <v>33</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
@@ -1151,13 +1337,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S16" s="9">
-        <v>310</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
@@ -1165,22 +1351,22 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C17" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-27</v>
+        <v>-14</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>33</v>
@@ -1189,16 +1375,16 @@
         <v>33</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>27</v>
@@ -1216,7 +1402,7 @@
         <v>37</v>
       </c>
       <c r="S17" s="9">
-        <v>210</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="18">
@@ -1227,19 +1413,19 @@
         <v>46167</v>
       </c>
       <c r="C18" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D18" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="G18" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>33</v>
@@ -1248,16 +1434,16 @@
         <v>33</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>27</v>
@@ -1272,10 +1458,10 @@
         <v>23</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="S18" s="9">
-        <v>61.21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1295,10 +1481,10 @@
         <v>46097</v>
       </c>
       <c r="F19" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G19" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>33</v>
@@ -1354,10 +1540,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G20" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>33</v>
@@ -1413,10 +1599,10 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G21" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>33</v>
@@ -1472,10 +1658,10 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G22" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>33</v>
@@ -1522,19 +1708,19 @@
         <v>46167</v>
       </c>
       <c r="C23" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D23" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G23" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>33</v>
@@ -1552,7 +1738,7 @@
         <v>47</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1570,7 +1756,7 @@
         <v>37</v>
       </c>
       <c r="S23" s="9">
-        <v>400</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="24">
@@ -1581,19 +1767,19 @@
         <v>46167</v>
       </c>
       <c r="C24" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D24" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E24" s="7">
+        <v>46119</v>
       </c>
       <c r="F24" s="8">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="G24" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>33</v>
@@ -1611,7 +1797,7 @@
         <v>49</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1623,13 +1809,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S24" s="9">
-        <v>572.72</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25">
@@ -1645,14 +1831,14 @@
       <c r="D25" s="7">
         <v>46167</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>23</v>
+      <c r="E25" s="7">
+        <v>46170</v>
       </c>
       <c r="F25" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G25" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>33</v>
@@ -1670,7 +1856,7 @@
         <v>51</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1682,13 +1868,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S25" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="26">
@@ -1705,13 +1891,13 @@
         <v>46167</v>
       </c>
       <c r="E26" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F26" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>33</v>
@@ -1726,10 +1912,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1747,7 +1933,7 @@
         <v>37</v>
       </c>
       <c r="S26" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27">
@@ -1764,13 +1950,13 @@
         <v>46167</v>
       </c>
       <c r="E27" s="7">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="F27" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G27" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>33</v>
@@ -1779,13 +1965,13 @@
         <v>33</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1803,10 +1989,10 @@
         <v>36</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28">
@@ -1823,13 +2009,13 @@
         <v>46167</v>
       </c>
       <c r="E28" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F28" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>33</v>
@@ -1838,16 +2024,16 @@
         <v>33</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -1865,7 +2051,7 @@
         <v>37</v>
       </c>
       <c r="S28" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29">
@@ -1873,7 +2059,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C29" s="7">
         <v>46167</v>
@@ -1881,11 +2067,11 @@
       <c r="D29" s="7">
         <v>46167</v>
       </c>
-      <c r="E29" s="7">
-        <v>46113</v>
+      <c r="E29" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G29" s="8">
         <v>-6</v>
@@ -1903,10 +2089,10 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -1918,13 +2104,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S29" s="9">
-        <v>680</v>
+        <v>262.56</v>
       </c>
     </row>
     <row r="30">
@@ -1932,7 +2118,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C30" s="7">
         <v>46167</v>
@@ -1940,14 +2126,14 @@
       <c r="D30" s="7">
         <v>46167</v>
       </c>
-      <c r="E30" s="7">
-        <v>46164</v>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G30" s="8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>33</v>
@@ -1956,13 +2142,13 @@
         <v>33</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -1977,13 +2163,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S30" s="9">
-        <v>680</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
@@ -1991,7 +2177,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C31" s="7">
         <v>46167</v>
@@ -1999,14 +2185,14 @@
       <c r="D31" s="7">
         <v>46167</v>
       </c>
-      <c r="E31" s="7">
-        <v>46167</v>
+      <c r="E31" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G31" s="8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>33</v>
@@ -2015,13 +2201,13 @@
         <v>33</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2036,13 +2222,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="32">
@@ -2050,19 +2236,19 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C32" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D32" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-20</v>
+        <v>-7</v>
       </c>
       <c r="G32" s="8">
         <v>-5</v>
@@ -2074,16 +2260,16 @@
         <v>33</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2098,10 +2284,10 @@
         <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S32" s="9">
-        <v>13.43</v>
+        <v>306.75</v>
       </c>
     </row>
     <row r="33">
@@ -2109,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="C33" s="7">
         <v>46167</v>
@@ -2121,10 +2307,10 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G33" s="8">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>33</v>
@@ -2133,13 +2319,13 @@
         <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2151,7 +2337,7 @@
         <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>23</v>
@@ -2160,7 +2346,7 @@
         <v>37</v>
       </c>
       <c r="S33" s="9">
-        <v>262.56</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34">
@@ -2168,19 +2354,19 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C34" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D34" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G34" s="8">
         <v>-4</v>
@@ -2192,13 +2378,13 @@
         <v>33</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2219,7 +2405,7 @@
         <v>37</v>
       </c>
       <c r="S34" s="9">
-        <v>220</v>
+        <v>233.82</v>
       </c>
     </row>
     <row r="35">
@@ -2227,22 +2413,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="C35" s="7">
-        <v>46167</v>
+        <v>45930</v>
       </c>
       <c r="D35" s="7">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="G35" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>33</v>
@@ -2251,13 +2437,13 @@
         <v>33</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2275,10 +2461,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="S35" s="9">
-        <v>301.57</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="36">
@@ -2286,58 +2472,58 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="C36" s="7">
-        <v>46167</v>
+        <v>46143</v>
       </c>
       <c r="D36" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46153</v>
       </c>
       <c r="F36" s="8">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S36" s="9">
-        <v>306.75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -2345,46 +2531,46 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C37" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D37" s="7">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-27</v>
+        <v>-7</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>23</v>
@@ -2396,7 +2582,7 @@
         <v>37</v>
       </c>
       <c r="S37" s="9">
-        <v>79.12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -2404,58 +2590,58 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C38" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D38" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E38" s="7">
         <v>46167</v>
       </c>
-      <c r="D38" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="F38" s="8">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S38" s="9">
-        <v>220</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -2463,46 +2649,46 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C39" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="D39" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>23</v>
@@ -2511,10 +2697,10 @@
         <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="S39" s="9">
-        <v>233.82</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
@@ -2522,28 +2708,28 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C40" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D40" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-6</v>
+        <v>-21</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>76</v>
@@ -2552,16 +2738,16 @@
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
@@ -2573,7 +2759,7 @@
         <v>37</v>
       </c>
       <c r="S40" s="9">
-        <v>370</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="41">
@@ -2581,81 +2767,2264 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="C41" s="7">
-        <v>45930</v>
+        <v>46082</v>
       </c>
       <c r="D41" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46097</v>
       </c>
       <c r="F41" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S41" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C42" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D42" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="8">
+        <v>-7</v>
+      </c>
+      <c r="G42" s="8">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="M41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S41" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="42" ht="23" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="13">
-        <f>SUM(S6:S41)</f>
+      <c r="M42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S42" s="9">
+        <v>393.43</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D43" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="8">
+        <v>-7</v>
+      </c>
+      <c r="G43" s="8">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S43" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D44" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0</v>
+      </c>
+      <c r="G44" s="8">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S44" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D45" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S45" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D46" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F46" s="8">
+        <v>0</v>
+      </c>
+      <c r="G46" s="8">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S46" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S47" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D48" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S48" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D49" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S49" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D50" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F50" s="8">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S50" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D51" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S51" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D52" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46163</v>
+      </c>
+      <c r="F52" s="8">
+        <v>0</v>
+      </c>
+      <c r="G52" s="8">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S52" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D53" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S53" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F54" s="8">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S54" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D55" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S55" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S56" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S57" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S58" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S59" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S60" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S61" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F62" s="8">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S62" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S63" s="9">
+        <v>676.84</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S64" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S65" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F66" s="8">
+        <v>0</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S66" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0</v>
+      </c>
+      <c r="G67" s="8">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S67" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="8">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S68" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S69" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S70" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F71" s="8">
+        <v>0</v>
+      </c>
+      <c r="G71" s="8">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S71" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F72" s="8">
+        <v>0</v>
+      </c>
+      <c r="G72" s="8">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S72" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46129</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0</v>
+      </c>
+      <c r="G73" s="8">
+        <v>0</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="S73" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F74" s="8">
+        <v>0</v>
+      </c>
+      <c r="G74" s="8">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="S74" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F75" s="8">
+        <v>0</v>
+      </c>
+      <c r="G75" s="8">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q75" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S75" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F76" s="8">
+        <v>0</v>
+      </c>
+      <c r="G76" s="8">
+        <v>0</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S76" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F77" s="8">
+        <v>0</v>
+      </c>
+      <c r="G77" s="8">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q77" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S77" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F78" s="8">
+        <v>0</v>
+      </c>
+      <c r="G78" s="8">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S78" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="79" ht="23" customHeight="1">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="13">
+        <f>SUM(S6:S78)</f>
       </c>
     </row>
   </sheetData>
